--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_46.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5458743.186270343</v>
+        <v>5458867.606899289</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13446283.47431926</v>
+        <v>13446283.47431917</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13446283.47431926</v>
+        <v>13446283.47431917</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1363764.72545305</v>
+        <v>1363764.725453003</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1363764.72545305</v>
+        <v>1363764.725453003</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40410103.14465346</v>
+        <v>40410103.14465351</v>
       </c>
     </row>
   </sheetData>
@@ -657,13 +657,13 @@
         <v>76.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>44.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>5.339155739849787</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>5.684341886080801e-14</v>
@@ -708,7 +708,7 @@
         <v>82.06148438523746</v>
       </c>
       <c r="T2" t="n">
-        <v>174.5775207628988</v>
+        <v>130.1029425199049</v>
       </c>
       <c r="U2" t="n">
         <v>244.1939598651936</v>
@@ -784,25 +784,25 @@
         <v>130.922287858417</v>
       </c>
       <c r="S3" t="n">
-        <v>58.16800939857359</v>
+        <v>344</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>314.5852107119142</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="V3" t="n">
         <v>9.510667191520156</v>
       </c>
       <c r="W3" t="n">
-        <v>298.6530836685567</v>
+        <v>27.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>344</v>
+        <v>14.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -900,7 +900,7 @@
         <v>5.339155739849787</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="F5" t="n">
         <v>5.684341886080801e-14</v>
@@ -979,7 +979,7 @@
         <v>344</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>210.8315745705938</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,19 +1018,19 @@
         <v>149.7411518829324</v>
       </c>
       <c r="R6" t="n">
+        <v>186.0185817926842</v>
+      </c>
+      <c r="S6" t="n">
+        <v>58.16800939857357</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>344</v>
-      </c>
-      <c r="S6" t="n">
-        <v>102.8354013484187</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9.510667191520156</v>
       </c>
       <c r="W6" t="n">
         <v>27.37314290982852</v>
@@ -1137,13 +1137,13 @@
         <v>5.339155739849787</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3735899370698406</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.3735899370891816</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>82.06148438523748</v>
+        <v>82.06148438523746</v>
       </c>
       <c r="T8" t="n">
         <v>180.1797525828352</v>
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>210.8315745705938</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,19 +1255,19 @@
         <v>149.7411518829324</v>
       </c>
       <c r="R9" t="n">
-        <v>227.3843853655845</v>
+        <v>130.922287858417</v>
       </c>
       <c r="S9" t="n">
-        <v>58.16800939857357</v>
+        <v>58.16800939857359</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>290.3782685048794</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9.510667191520156</v>
+        <v>357.0000000000005</v>
       </c>
       <c r="W9" t="n">
         <v>27.37314290982852</v>
@@ -1276,7 +1276,7 @@
         <v>14.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>357.0000000000005</v>
       </c>
     </row>
     <row r="10">
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.60448025500889</v>
+        <v>91.60448025500892</v>
       </c>
       <c r="N10" t="n">
         <v>142.7292555995538</v>
@@ -1328,7 +1328,7 @@
         <v>213.7803181773756</v>
       </c>
       <c r="P10" t="n">
-        <v>263.9095366725398</v>
+        <v>263.9095366725397</v>
       </c>
       <c r="Q10" t="n">
         <v>308.004266425598</v>
@@ -1422,13 +1422,13 @@
         <v>190.1797525828352</v>
       </c>
       <c r="U11" t="n">
-        <v>254.1939598651936</v>
+        <v>129.031231652666</v>
       </c>
       <c r="V11" t="n">
         <v>234.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>118.2107477683723</v>
+        <v>243.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>197.2818334606677</v>
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>360.0000000000023</v>
+        <v>360.0000000000037</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>210.8315745705938</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>9.620831255249666</v>
       </c>
       <c r="U12" t="n">
-        <v>5.198331458299955</v>
+        <v>44.66499993935407</v>
       </c>
       <c r="V12" t="n">
         <v>19.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>197.9735588220097</v>
+        <v>37.37314290982852</v>
       </c>
       <c r="X12" t="n">
         <v>24.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>360.0000000000023</v>
+        <v>4.391392766134345</v>
       </c>
     </row>
     <row r="13">
@@ -1556,7 +1556,7 @@
         <v>5.759267502041467</v>
       </c>
       <c r="M13" t="n">
-        <v>98.19519485485489</v>
+        <v>101.6044802550089</v>
       </c>
       <c r="N13" t="n">
         <v>152.7292555995538</v>
@@ -1568,7 +1568,7 @@
         <v>273.9095366725398</v>
       </c>
       <c r="Q13" t="n">
-        <v>318.004266425598</v>
+        <v>314.5949810254921</v>
       </c>
       <c r="R13" t="n">
         <v>324.7101607680363</v>
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86.99931295557451</v>
+        <v>68.82903687553603</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>15.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>58.55205256530123</v>
+        <v>92.06148438523746</v>
       </c>
       <c r="T14" t="n">
         <v>190.1797525828352</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>55.10554379345876</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1690,13 +1690,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>325.5567056863481</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>149.7411518829324</v>
       </c>
       <c r="R15" t="n">
-        <v>220.0978403288686</v>
+        <v>360.0000000000051</v>
       </c>
       <c r="S15" t="n">
         <v>68.16800939857359</v>
@@ -1741,10 +1741,10 @@
         <v>5.198331458299947</v>
       </c>
       <c r="V15" t="n">
-        <v>19.51066719152016</v>
+        <v>360.0000000000032</v>
       </c>
       <c r="W15" t="n">
-        <v>37.37314290982852</v>
+        <v>360.0000000000032</v>
       </c>
       <c r="X15" t="n">
         <v>24.86273944538755</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.349982101887478</v>
+        <v>2.3499821019352</v>
       </c>
       <c r="M16" t="n">
         <v>101.6044802550089</v>
@@ -1845,7 +1845,7 @@
         <v>45.47457824299391</v>
       </c>
       <c r="D17" t="n">
-        <v>6.592091271577013</v>
+        <v>6.339155739849787</v>
       </c>
       <c r="E17" t="n">
         <v>0.3632896068686478</v>
@@ -1860,7 +1860,7 @@
         <v>0.5101360904620833</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.2529355317719425</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,22 +1921,22 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>360.0000000000023</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>325.5567056863481</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>330.40233246944</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1978,16 +1978,16 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>173.5550938865827</v>
+        <v>10.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>360.0000000000014</v>
+        <v>28.37314290982852</v>
       </c>
       <c r="X18" t="n">
         <v>15.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>103.0563927054864</v>
       </c>
     </row>
     <row r="19">
@@ -2085,7 +2085,7 @@
         <v>6.339155739849787</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3632896068686478</v>
+        <v>0.6162251386414908</v>
       </c>
       <c r="F20" t="n">
         <v>0.8896287080118555</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2529355317270597</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>83.06148438523746</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>292.9514831603869</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>360.0000000000015</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>10.51066719152016</v>
+        <v>360.0000000000024</v>
       </c>
       <c r="W21" t="n">
-        <v>28.37314290982852</v>
+        <v>335.6357196048704</v>
       </c>
       <c r="X21" t="n">
-        <v>15.86273944538755</v>
+        <v>360.0000000000024</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2529355317270597</v>
+        <v>0.2529355317707291</v>
       </c>
       <c r="S23" t="n">
         <v>83.06148438523748</v>
@@ -2395,13 +2395,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>310.2793859385281</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>149.7411518829324</v>
+        <v>-4.276898835087195e-12</v>
       </c>
       <c r="R24" t="n">
         <v>131.922287858417</v>
@@ -2449,16 +2449,16 @@
         <v>0.6208312552496649</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>125.3768714877985</v>
       </c>
       <c r="V24" t="n">
-        <v>10.51066719152016</v>
+        <v>360.0000000000031</v>
       </c>
       <c r="W24" t="n">
-        <v>28.37314290982852</v>
+        <v>360.0000000000031</v>
       </c>
       <c r="X24" t="n">
-        <v>15.86273944538755</v>
+        <v>360.0000000000031</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2550,22 +2550,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>167.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>96.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>60.10677121381438</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>89.41566374430265</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>90.51013609046208</v>
@@ -2601,25 +2601,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>173.0614843852375</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>103.3717376429581</v>
+        <v>335.1939598651936</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>315.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>324.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>278.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>197.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2635,7 +2635,7 @@
         <v>47.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>165.3815509091657</v>
+        <v>33.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>28.67209722191262</v>
@@ -2680,7 +2680,7 @@
         <v>221.922287858417</v>
       </c>
       <c r="S27" t="n">
-        <v>149.1680093985736</v>
+        <v>280.6118734100844</v>
       </c>
       <c r="T27" t="n">
         <v>90.62083125524967</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>86.75926750204147</v>
       </c>
       <c r="M28" t="n">
         <v>182.6044802550089</v>
@@ -2747,19 +2747,19 @@
         <v>233.7292555995538</v>
       </c>
       <c r="O28" t="n">
-        <v>304.7803181773756</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>341</v>
+        <v>92.55754644876019</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="R28" t="n">
-        <v>261.2387459680617</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>45.70225019465872</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>90.51013609046208</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2838,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>173.0614843852375</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>271.1797525828352</v>
+        <v>257.4242038966209</v>
       </c>
       <c r="U29" t="n">
         <v>335.1939598651936</v>
@@ -2850,7 +2850,7 @@
         <v>315.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>228.0665789999098</v>
+        <v>324.3734759809475</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>16.40233246944</v>
       </c>
       <c r="I30" t="n">
-        <v>131.4438640114631</v>
+        <v>131.4438640115109</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>86.75926750204147</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>182.6044802550089</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>233.7292555995538</v>
@@ -2987,16 +2987,16 @@
         <v>304.7803181773756</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="Q31" t="n">
-        <v>128.7772282713614</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="R31" t="n">
-        <v>341</v>
+        <v>102.8432262230938</v>
       </c>
       <c r="S31" t="n">
-        <v>45.70225019465872</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>77.62009580865764</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>149.7411518829324</v>
       </c>
       <c r="R33" t="n">
-        <v>328.0000000000051</v>
+        <v>118.922287858417</v>
       </c>
       <c r="S33" t="n">
         <v>46.16800939857357</v>
@@ -3160,19 +3160,19 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="W33" t="n">
-        <v>15.37314290982852</v>
+        <v>299.2082114146895</v>
       </c>
       <c r="X33" t="n">
-        <v>328.0000000000014</v>
+        <v>2.862739445387547</v>
       </c>
       <c r="Y33" t="n">
-        <v>328.0000000000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3264,7 +3264,7 @@
         <v>63.99931295557451</v>
       </c>
       <c r="C35" t="n">
-        <v>31.47457824299391</v>
+        <v>30.00172391991344</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>67.58863006215704</v>
+        <v>69.06148438523748</v>
       </c>
       <c r="T35" t="n">
         <v>167.1797525828352</v>
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>296.5658114146894</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>117.922287858417</v>
       </c>
       <c r="S36" t="n">
-        <v>45.16800939857359</v>
+        <v>45.16800939857357</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>325</v>
+        <v>14.37314290982852</v>
       </c>
       <c r="X36" t="n">
         <v>1.862739445387547</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>282.1926685048609</v>
       </c>
     </row>
     <row r="37">
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>78.60448025500892</v>
+        <v>78.60448025500889</v>
       </c>
       <c r="N37" t="n">
         <v>129.7292555995538</v>
@@ -3461,7 +3461,7 @@
         <v>200.7803181773756</v>
       </c>
       <c r="P37" t="n">
-        <v>250.9095366725397</v>
+        <v>250.9095366725398</v>
       </c>
       <c r="Q37" t="n">
         <v>295.004266425598</v>
@@ -3586,10 +3586,10 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>152.1018297863669</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,13 +3622,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>149.7411518829324</v>
       </c>
       <c r="R39" t="n">
         <v>117.922287858417</v>
       </c>
       <c r="S39" t="n">
-        <v>325</v>
+        <v>45.16800939857357</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3637,16 +3637,16 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>14.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>1.862739445387547</v>
+        <v>284.0554079502484</v>
       </c>
       <c r="Y39" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>172.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>95.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>63.23820070890464</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3786,22 +3786,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>14.22922325029306</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>276.1797525828352</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>325.00000000003</v>
       </c>
       <c r="V41" t="n">
         <v>320.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>325.0000000000174</v>
+        <v>325.0000000000176</v>
       </c>
       <c r="X41" t="n">
-        <v>283.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>221.2733518699075</v>
+        <v>221.2733518698802</v>
       </c>
       <c r="S42" t="n">
         <v>154.1680093985736</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>91.75926750204147</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>140.0279262925914</v>
+        <v>309.7803181773756</v>
       </c>
       <c r="P43" t="n">
-        <v>325.0000000000625</v>
+        <v>247.0068756173299</v>
       </c>
       <c r="Q43" t="n">
-        <v>325.0000000000614</v>
+        <v>325.0000000000555</v>
       </c>
       <c r="R43" t="n">
-        <v>325.0000000000618</v>
+        <v>325.0000000000578</v>
       </c>
       <c r="S43" t="n">
         <v>50.70225019465872</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>172.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>128.7421261104684</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>101.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>95.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>95.88962870801186</v>
       </c>
       <c r="G44" t="n">
         <v>94.41566374430266</v>
       </c>
       <c r="H44" t="n">
-        <v>50.31327684361553</v>
+        <v>95.51013609046208</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4029,19 +4029,19 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>325.0000000000259</v>
       </c>
       <c r="V44" t="n">
-        <v>320.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>325.0000000000083</v>
+        <v>325.0000000000106</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>202.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>221.2733518698802</v>
+        <v>226.922287858417</v>
       </c>
       <c r="S45" t="n">
         <v>154.1680093985736</v>
@@ -4114,7 +4114,7 @@
         <v>105.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>123.3731429098285</v>
+        <v>117.7242069212915</v>
       </c>
       <c r="X45" t="n">
         <v>110.8627394453875</v>
@@ -4163,25 +4163,25 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>187.6044802550089</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>44.18271353964039</v>
+        <v>309.7803181773756</v>
       </c>
       <c r="P46" t="n">
-        <v>325.0000000000565</v>
+        <v>325</v>
       </c>
       <c r="Q46" t="n">
-        <v>325.0000000000564</v>
+        <v>297.709125812102</v>
       </c>
       <c r="R46" t="n">
-        <v>325.0000000000568</v>
+        <v>325</v>
       </c>
       <c r="S46" t="n">
-        <v>50.70225019465869</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.91308660590887</v>
+        <v>77.83690301297344</v>
       </c>
       <c r="C2" t="n">
         <v>32.91308660590887</v>
@@ -4321,25 +4321,25 @@
         <v>27.52</v>
       </c>
       <c r="J2" t="n">
-        <v>368.08</v>
+        <v>300.9350708542715</v>
       </c>
       <c r="K2" t="n">
-        <v>411.1119419597989</v>
+        <v>641.4950708542715</v>
       </c>
       <c r="L2" t="n">
-        <v>464.4968711055276</v>
+        <v>694.8800000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>805.0568711055276</v>
+        <v>694.8800000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>1145.616871105528</v>
+        <v>1035.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1145.616871105528</v>
+        <v>1035.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1193.979416087364</v>
+        <v>1376</v>
       </c>
       <c r="Q2" t="n">
         <v>1376</v>
@@ -4351,22 +4351,22 @@
         <v>1293.109611732083</v>
       </c>
       <c r="T2" t="n">
-        <v>1116.768681668549</v>
+        <v>1161.692498075614</v>
       </c>
       <c r="U2" t="n">
-        <v>870.1081161481515</v>
+        <v>915.031932555216</v>
       </c>
       <c r="V2" t="n">
-        <v>642.985869514996</v>
+        <v>687.9096859220606</v>
       </c>
       <c r="W2" t="n">
-        <v>407.255085695857</v>
+        <v>452.1789021029216</v>
       </c>
       <c r="X2" t="n">
-        <v>218.0815165436674</v>
+        <v>263.0053329507319</v>
       </c>
       <c r="Y2" t="n">
-        <v>110.6901703994185</v>
+        <v>155.613986806483</v>
       </c>
     </row>
     <row r="3">
@@ -4400,22 +4400,22 @@
         <v>27.52</v>
       </c>
       <c r="J3" t="n">
-        <v>168.5772291375631</v>
+        <v>105.4301337690276</v>
       </c>
       <c r="K3" t="n">
-        <v>386.9978806093051</v>
+        <v>323.8507852407695</v>
       </c>
       <c r="L3" t="n">
-        <v>697.6487738082787</v>
+        <v>634.5016784397432</v>
       </c>
       <c r="M3" t="n">
-        <v>829.5910655511379</v>
+        <v>766.4439701826024</v>
       </c>
       <c r="N3" t="n">
-        <v>1009.94692421531</v>
+        <v>946.7998288467744</v>
       </c>
       <c r="O3" t="n">
-        <v>1292.054329200916</v>
+        <v>1228.90723383238</v>
       </c>
       <c r="P3" t="n">
         <v>1376</v>
@@ -4427,22 +4427,22 @@
         <v>1092.501576018839</v>
       </c>
       <c r="S3" t="n">
-        <v>1033.746010969775</v>
+        <v>745.0268285440914</v>
       </c>
       <c r="T3" t="n">
-        <v>1033.746010969775</v>
+        <v>427.2639894411477</v>
       </c>
       <c r="U3" t="n">
-        <v>1033.746010969775</v>
+        <v>79.78924196640023</v>
       </c>
       <c r="V3" t="n">
-        <v>1024.139276432886</v>
+        <v>70.18250742951118</v>
       </c>
       <c r="W3" t="n">
-        <v>722.469494949495</v>
+        <v>42.53286812665409</v>
       </c>
       <c r="X3" t="n">
-        <v>374.9947474747475</v>
+        <v>27.52</v>
       </c>
       <c r="Y3" t="n">
         <v>27.52</v>
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>646.6511314641751</v>
+        <v>305.2605201641875</v>
       </c>
       <c r="C4" t="n">
-        <v>777.6031372826109</v>
+        <v>436.2125259826233</v>
       </c>
       <c r="D4" t="n">
-        <v>895.8722814076109</v>
+        <v>554.4816701076234</v>
       </c>
       <c r="E4" t="n">
-        <v>1018.651185619024</v>
+        <v>677.2605743190364</v>
       </c>
       <c r="F4" t="n">
-        <v>1147.962158210959</v>
+        <v>806.571546910972</v>
       </c>
       <c r="G4" t="n">
-        <v>1306.470469999484</v>
+        <v>965.0798586994965</v>
       </c>
       <c r="H4" t="n">
-        <v>1375.740220099103</v>
+        <v>1140.895602875288</v>
       </c>
       <c r="I4" t="n">
-        <v>1375.740220099103</v>
+        <v>1371.541894926125</v>
       </c>
       <c r="J4" t="n">
-        <v>1375.740220099103</v>
+        <v>1371.541894926125</v>
       </c>
       <c r="K4" t="n">
-        <v>1375.740220099103</v>
+        <v>1371.541894926125</v>
       </c>
       <c r="L4" t="n">
         <v>1375.740220099103</v>
@@ -4509,22 +4509,22 @@
         <v>72.36477230728789</v>
       </c>
       <c r="T4" t="n">
-        <v>266.0388203185518</v>
+        <v>72.36477230728789</v>
       </c>
       <c r="U4" t="n">
-        <v>266.0388203185518</v>
+        <v>72.36477230728789</v>
       </c>
       <c r="V4" t="n">
-        <v>469.8102132044977</v>
+        <v>149.2797291399939</v>
       </c>
       <c r="W4" t="n">
-        <v>646.6511314641751</v>
+        <v>149.2797291399939</v>
       </c>
       <c r="X4" t="n">
-        <v>646.6511314641751</v>
+        <v>305.2605201641875</v>
       </c>
       <c r="Y4" t="n">
-        <v>646.6511314641751</v>
+        <v>305.2605201641875</v>
       </c>
     </row>
     <row r="5">
@@ -4567,16 +4567,16 @@
         <v>464.4968711055276</v>
       </c>
       <c r="M5" t="n">
-        <v>646.5174550181641</v>
+        <v>805.0568711055276</v>
       </c>
       <c r="N5" t="n">
-        <v>987.0774550181641</v>
+        <v>1145.616871105528</v>
       </c>
       <c r="O5" t="n">
-        <v>987.0774550181641</v>
+        <v>1145.616871105528</v>
       </c>
       <c r="P5" t="n">
-        <v>1035.44</v>
+        <v>1193.979416087364</v>
       </c>
       <c r="Q5" t="n">
         <v>1376</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>721.128179012033</v>
+        <v>587.9559339096908</v>
       </c>
       <c r="C6" t="n">
-        <v>721.128179012033</v>
+        <v>587.9559339096908</v>
       </c>
       <c r="D6" t="n">
-        <v>373.6534315372855</v>
+        <v>240.4811864349433</v>
       </c>
       <c r="E6" t="n">
-        <v>27.52</v>
+        <v>240.4811864349433</v>
       </c>
       <c r="F6" t="n">
-        <v>27.52</v>
+        <v>240.4811864349433</v>
       </c>
       <c r="G6" t="n">
-        <v>27.52</v>
+        <v>240.4811864349433</v>
       </c>
       <c r="H6" t="n">
-        <v>27.52</v>
+        <v>240.4811864349433</v>
       </c>
       <c r="I6" t="n">
         <v>27.52</v>
@@ -4643,7 +4643,7 @@
         <v>386.9978806093051</v>
       </c>
       <c r="L6" t="n">
-        <v>697.6487738082787</v>
+        <v>634.5016784397432</v>
       </c>
       <c r="M6" t="n">
         <v>766.4439701826024</v>
@@ -4661,28 +4661,28 @@
         <v>1224.746311229361</v>
       </c>
       <c r="R6" t="n">
-        <v>877.2715637546137</v>
+        <v>1036.848753863014</v>
       </c>
       <c r="S6" t="n">
-        <v>773.3974209784332</v>
+        <v>978.0931888139494</v>
       </c>
       <c r="T6" t="n">
-        <v>773.3974209784332</v>
+        <v>978.0931888139494</v>
       </c>
       <c r="U6" t="n">
-        <v>773.3974209784332</v>
+        <v>978.0931888139494</v>
       </c>
       <c r="V6" t="n">
-        <v>763.7906864415442</v>
+        <v>630.6184413392019</v>
       </c>
       <c r="W6" t="n">
-        <v>736.1410471386871</v>
+        <v>602.9688020363449</v>
       </c>
       <c r="X6" t="n">
-        <v>721.128179012033</v>
+        <v>587.9559339096908</v>
       </c>
       <c r="Y6" t="n">
-        <v>721.128179012033</v>
+        <v>587.9559339096908</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85.1754465896357</v>
+        <v>27.52</v>
       </c>
       <c r="C7" t="n">
-        <v>85.1754465896357</v>
+        <v>99.85085115560231</v>
       </c>
       <c r="D7" t="n">
-        <v>85.1754465896357</v>
+        <v>218.1199952806024</v>
       </c>
       <c r="E7" t="n">
-        <v>207.9543508010487</v>
+        <v>340.8988994920154</v>
       </c>
       <c r="F7" t="n">
-        <v>337.2653233929842</v>
+        <v>470.2098720839509</v>
       </c>
       <c r="G7" t="n">
-        <v>495.7736351815088</v>
+        <v>628.7181838724755</v>
       </c>
       <c r="H7" t="n">
-        <v>671.5893793572998</v>
+        <v>804.5339280482665</v>
       </c>
       <c r="I7" t="n">
-        <v>902.2356714081368</v>
+        <v>1035.180220099104</v>
       </c>
       <c r="J7" t="n">
-        <v>1242.795671408137</v>
+        <v>1375.740220099103</v>
       </c>
       <c r="K7" t="n">
         <v>1375.740220099103</v>
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79.25426658577132</v>
+        <v>79.25426658579178</v>
       </c>
       <c r="C8" t="n">
-        <v>34.33045017870676</v>
+        <v>34.33045017872722</v>
       </c>
       <c r="D8" t="n">
-        <v>28.93736357279788</v>
+        <v>28.93736357281834</v>
       </c>
       <c r="E8" t="n">
-        <v>28.56000000000006</v>
+        <v>28.93736357281834</v>
       </c>
       <c r="F8" t="n">
-        <v>28.56</v>
+        <v>28.93736357281834</v>
       </c>
       <c r="G8" t="n">
-        <v>28.56</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="H8" t="n">
-        <v>28.56</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="I8" t="n">
-        <v>28.56</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="J8" t="n">
-        <v>381.9900000000001</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="K8" t="n">
-        <v>425.0219419597991</v>
+        <v>71.59194195979998</v>
       </c>
       <c r="L8" t="n">
-        <v>478.4068711055277</v>
+        <v>319.3474550181832</v>
       </c>
       <c r="M8" t="n">
-        <v>672.7774550181639</v>
+        <v>672.7774550181837</v>
       </c>
       <c r="N8" t="n">
-        <v>1026.207455018164</v>
+        <v>1026.207455018184</v>
       </c>
       <c r="O8" t="n">
-        <v>1026.207455018164</v>
+        <v>1026.207455018184</v>
       </c>
       <c r="P8" t="n">
-        <v>1074.57</v>
+        <v>1074.57000000002</v>
       </c>
       <c r="Q8" t="n">
-        <v>1428</v>
+        <v>1428.000000000021</v>
       </c>
       <c r="R8" t="n">
-        <v>1428</v>
+        <v>1428.000000000021</v>
       </c>
       <c r="S8" t="n">
-        <v>1345.109611732083</v>
+        <v>1345.109611732104</v>
       </c>
       <c r="T8" t="n">
-        <v>1163.109861648411</v>
+        <v>1163.109861648432</v>
       </c>
       <c r="U8" t="n">
-        <v>916.4492961280139</v>
+        <v>916.4492961280343</v>
       </c>
       <c r="V8" t="n">
-        <v>689.3270494948584</v>
+        <v>689.3270494948789</v>
       </c>
       <c r="W8" t="n">
-        <v>453.5962656757195</v>
+        <v>453.5962656757399</v>
       </c>
       <c r="X8" t="n">
-        <v>264.4226965235298</v>
+        <v>264.4226965235503</v>
       </c>
       <c r="Y8" t="n">
-        <v>157.0313503792809</v>
+        <v>157.0313503793014</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>936.0403068749226</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="C9" t="n">
-        <v>936.0403068749226</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="D9" t="n">
-        <v>584.5880978873442</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="E9" t="n">
-        <v>584.5880978873442</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="F9" t="n">
-        <v>241.5211864349433</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="G9" t="n">
-        <v>241.5211864349433</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="H9" t="n">
-        <v>241.5211864349433</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="I9" t="n">
-        <v>28.56</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="J9" t="n">
-        <v>157.4301337690276</v>
+        <v>169.6172291375641</v>
       </c>
       <c r="K9" t="n">
-        <v>375.8507852407695</v>
+        <v>388.0378806093061</v>
       </c>
       <c r="L9" t="n">
-        <v>686.5016784397432</v>
+        <v>698.6887738082797</v>
       </c>
       <c r="M9" t="n">
-        <v>818.4439701826024</v>
+        <v>830.6310655511389</v>
       </c>
       <c r="N9" t="n">
-        <v>998.7998288467744</v>
+        <v>1010.986924215311</v>
       </c>
       <c r="O9" t="n">
-        <v>1280.90723383238</v>
+        <v>1293.094329200917</v>
       </c>
       <c r="P9" t="n">
-        <v>1428</v>
+        <v>1428.000000000021</v>
       </c>
       <c r="Q9" t="n">
-        <v>1276.746311229361</v>
+        <v>1276.746311229382</v>
       </c>
       <c r="R9" t="n">
-        <v>1047.065113890387</v>
+        <v>1144.50157601886</v>
       </c>
       <c r="S9" t="n">
-        <v>988.3095488413228</v>
+        <v>1085.746010969795</v>
       </c>
       <c r="T9" t="n">
-        <v>988.3095488413228</v>
+        <v>792.4346286416344</v>
       </c>
       <c r="U9" t="n">
-        <v>988.3095488413228</v>
+        <v>792.4346286416344</v>
       </c>
       <c r="V9" t="n">
-        <v>978.7028143044338</v>
+        <v>431.8285680355733</v>
       </c>
       <c r="W9" t="n">
-        <v>951.0531750015767</v>
+        <v>404.1789287327162</v>
       </c>
       <c r="X9" t="n">
-        <v>936.0403068749226</v>
+        <v>389.1660606060621</v>
       </c>
       <c r="Y9" t="n">
-        <v>936.0403068749226</v>
+        <v>28.56000000000099</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>886.2073462351577</v>
+        <v>1243.403258213873</v>
       </c>
       <c r="C10" t="n">
-        <v>886.2073462351577</v>
+        <v>1374.355264032309</v>
       </c>
       <c r="D10" t="n">
-        <v>886.2073462351577</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="E10" t="n">
-        <v>886.2073462351577</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="F10" t="n">
-        <v>886.2073462351577</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="G10" t="n">
-        <v>886.2073462351577</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="H10" t="n">
-        <v>886.2073462351577</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="I10" t="n">
-        <v>886.2073462351577</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="J10" t="n">
-        <v>1239.637346235158</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="K10" t="n">
-        <v>1372.581894926125</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="L10" t="n">
-        <v>1376.780220099103</v>
+        <v>1376.780220099104</v>
       </c>
       <c r="M10" t="n">
-        <v>1284.250442063741</v>
+        <v>1284.250442063742</v>
       </c>
       <c r="N10" t="n">
-        <v>1140.079476811666</v>
+        <v>1140.079476811667</v>
       </c>
       <c r="O10" t="n">
-        <v>924.139761480984</v>
+        <v>924.1397614809848</v>
       </c>
       <c r="P10" t="n">
-        <v>657.564471912762</v>
+        <v>657.5644719127629</v>
       </c>
       <c r="Q10" t="n">
-        <v>346.4490512808448</v>
+        <v>346.4490512808458</v>
       </c>
       <c r="R10" t="n">
-        <v>28.56</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="S10" t="n">
-        <v>73.40477230728787</v>
+        <v>28.56000000000099</v>
       </c>
       <c r="T10" t="n">
-        <v>233.2549433863086</v>
+        <v>222.2340480112649</v>
       </c>
       <c r="U10" t="n">
-        <v>233.2549433863086</v>
+        <v>473.7435176987319</v>
       </c>
       <c r="V10" t="n">
-        <v>437.0263362722545</v>
+        <v>677.5149105846779</v>
       </c>
       <c r="W10" t="n">
-        <v>613.867254531932</v>
+        <v>854.3558288443553</v>
       </c>
       <c r="X10" t="n">
-        <v>769.8480455561255</v>
+        <v>1010.336619868549</v>
       </c>
       <c r="Y10" t="n">
-        <v>886.2073462351577</v>
+        <v>1126.695920547581</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>136.8731839722111</v>
+        <v>136.873183972212</v>
       </c>
       <c r="C11" t="n">
-        <v>81.84835746413638</v>
+        <v>81.84835746413738</v>
       </c>
       <c r="D11" t="n">
-        <v>66.3542607572174</v>
+        <v>66.3542607572184</v>
       </c>
       <c r="E11" t="n">
-        <v>56.89639246745109</v>
+        <v>56.89639246745208</v>
       </c>
       <c r="F11" t="n">
-        <v>46.90686851996437</v>
+        <v>46.90686851996536</v>
       </c>
       <c r="G11" t="n">
-        <v>38.40619807117382</v>
+        <v>38.40619807117481</v>
       </c>
       <c r="H11" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I11" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J11" t="n">
-        <v>385.2000000000023</v>
+        <v>385.2000000000046</v>
       </c>
       <c r="K11" t="n">
-        <v>428.2319419598014</v>
+        <v>428.2319419598037</v>
       </c>
       <c r="L11" t="n">
-        <v>481.61687110553</v>
+        <v>481.6168711055324</v>
       </c>
       <c r="M11" t="n">
-        <v>838.0168711055323</v>
+        <v>838.016871105536</v>
       </c>
       <c r="N11" t="n">
-        <v>1194.416871105535</v>
+        <v>1194.41687110554</v>
       </c>
       <c r="O11" t="n">
-        <v>1194.416871105535</v>
+        <v>1194.41687110554</v>
       </c>
       <c r="P11" t="n">
-        <v>1242.779416087371</v>
+        <v>1242.779416087376</v>
       </c>
       <c r="Q11" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="R11" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="S11" t="n">
-        <v>1347.008601631073</v>
+        <v>1347.008601631122</v>
       </c>
       <c r="T11" t="n">
-        <v>1154.907841446391</v>
+        <v>1154.90784144644</v>
       </c>
       <c r="U11" t="n">
-        <v>898.1462658249836</v>
+        <v>1024.573264019505</v>
       </c>
       <c r="V11" t="n">
-        <v>660.923009090818</v>
+        <v>787.3500072853395</v>
       </c>
       <c r="W11" t="n">
-        <v>541.5182133651895</v>
+        <v>541.5182133651905</v>
       </c>
       <c r="X11" t="n">
-        <v>342.2436341119898</v>
+        <v>342.2436341119907</v>
       </c>
       <c r="Y11" t="n">
-        <v>224.7512778667308</v>
+        <v>224.7512778667318</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>241.7611864349433</v>
+        <v>723.3191204399803</v>
       </c>
       <c r="C12" t="n">
-        <v>241.7611864349433</v>
+        <v>723.3191204399803</v>
       </c>
       <c r="D12" t="n">
-        <v>241.7611864349433</v>
+        <v>371.8669114524019</v>
       </c>
       <c r="E12" t="n">
-        <v>241.7611864349433</v>
+        <v>371.8669114524019</v>
       </c>
       <c r="F12" t="n">
-        <v>241.7611864349433</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="G12" t="n">
-        <v>241.7611864349433</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="H12" t="n">
-        <v>241.7611864349433</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I12" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J12" t="n">
-        <v>169.8572291375631</v>
+        <v>169.8572291375641</v>
       </c>
       <c r="K12" t="n">
-        <v>388.277880609305</v>
+        <v>388.277880609306</v>
       </c>
       <c r="L12" t="n">
-        <v>698.9287738082787</v>
+        <v>698.9287738082796</v>
       </c>
       <c r="M12" t="n">
-        <v>830.8710655511379</v>
+        <v>830.8710655511388</v>
       </c>
       <c r="N12" t="n">
-        <v>1011.22692421531</v>
+        <v>1010.799828846824</v>
       </c>
       <c r="O12" t="n">
-        <v>1292.907233832437</v>
+        <v>1292.907233832429</v>
       </c>
       <c r="P12" t="n">
-        <v>1440.000000000057</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="Q12" t="n">
-        <v>1440.000000000057</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="R12" t="n">
-        <v>1297.654254688524</v>
+        <v>1297.654254688517</v>
       </c>
       <c r="S12" t="n">
-        <v>1228.79767953845</v>
+        <v>1228.797679538443</v>
       </c>
       <c r="T12" t="n">
-        <v>1219.079668169511</v>
+        <v>1219.079668169504</v>
       </c>
       <c r="U12" t="n">
-        <v>1213.828828312642</v>
+        <v>1173.963506614601</v>
       </c>
       <c r="V12" t="n">
-        <v>1194.121083674743</v>
+        <v>1154.255761976701</v>
       </c>
       <c r="W12" t="n">
-        <v>994.1477919353395</v>
+        <v>1116.505112572834</v>
       </c>
       <c r="X12" t="n">
-        <v>969.0339137076753</v>
+        <v>1091.39123434517</v>
       </c>
       <c r="Y12" t="n">
-        <v>605.3975500713093</v>
+        <v>1086.955484076348</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>589.6343941540566</v>
+        <v>316.6329009977745</v>
       </c>
       <c r="C13" t="n">
-        <v>589.6343941540566</v>
+        <v>437.6849068162103</v>
       </c>
       <c r="D13" t="n">
-        <v>698.0035382790567</v>
+        <v>546.0540509412103</v>
       </c>
       <c r="E13" t="n">
-        <v>810.8824424904697</v>
+        <v>658.9329551526233</v>
       </c>
       <c r="F13" t="n">
-        <v>930.2934150824052</v>
+        <v>778.3439277445589</v>
       </c>
       <c r="G13" t="n">
-        <v>930.2934150824052</v>
+        <v>926.9522395330835</v>
       </c>
       <c r="H13" t="n">
-        <v>1096.209159258196</v>
+        <v>1092.867983708874</v>
       </c>
       <c r="I13" t="n">
-        <v>1316.955451309033</v>
+        <v>1313.614275759711</v>
       </c>
       <c r="J13" t="n">
-        <v>1316.955451309033</v>
+        <v>1316.955451309081</v>
       </c>
       <c r="K13" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="L13" t="n">
-        <v>1434.182558078746</v>
+        <v>1434.182558078795</v>
       </c>
       <c r="M13" t="n">
-        <v>1334.995492568792</v>
+        <v>1331.551769942423</v>
       </c>
       <c r="N13" t="n">
-        <v>1180.723517215707</v>
+        <v>1177.279794589338</v>
       </c>
       <c r="O13" t="n">
-        <v>954.6827917840144</v>
+        <v>951.2390691576458</v>
       </c>
       <c r="P13" t="n">
-        <v>678.0064921147823</v>
+        <v>674.5627694884136</v>
       </c>
       <c r="Q13" t="n">
-        <v>356.7900613818549</v>
+        <v>356.7900613818559</v>
       </c>
       <c r="R13" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="S13" t="n">
-        <v>28.8</v>
+        <v>63.74477230728886</v>
       </c>
       <c r="T13" t="n">
-        <v>212.5740480112639</v>
+        <v>63.74477230728886</v>
       </c>
       <c r="U13" t="n">
-        <v>212.5740480112639</v>
+        <v>63.74477230728886</v>
       </c>
       <c r="V13" t="n">
-        <v>406.4454408972099</v>
+        <v>63.74477230728886</v>
       </c>
       <c r="W13" t="n">
-        <v>573.3863591568872</v>
+        <v>63.74477230728886</v>
       </c>
       <c r="X13" t="n">
-        <v>573.3863591568872</v>
+        <v>209.8255633314824</v>
       </c>
       <c r="Y13" t="n">
-        <v>573.3863591568872</v>
+        <v>209.8255633314824</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44.29409670691898</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="C14" t="n">
-        <v>44.29409670691898</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="D14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="E14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="F14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="G14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="H14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J14" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="K14" t="n">
-        <v>71.831941959799</v>
+        <v>385.2000000000132</v>
       </c>
       <c r="L14" t="n">
-        <v>322.4374550181583</v>
+        <v>438.5849291457419</v>
       </c>
       <c r="M14" t="n">
-        <v>678.8374550181602</v>
+        <v>794.9849291457451</v>
       </c>
       <c r="N14" t="n">
-        <v>1035.237455018162</v>
+        <v>1151.384929145748</v>
       </c>
       <c r="O14" t="n">
-        <v>1035.237455018162</v>
+        <v>1151.384929145748</v>
       </c>
       <c r="P14" t="n">
-        <v>1083.599999999998</v>
+        <v>1199.747474127584</v>
       </c>
       <c r="Q14" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="R14" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="S14" t="n">
-        <v>1380.856512560302</v>
+        <v>1347.008601631123</v>
       </c>
       <c r="T14" t="n">
-        <v>1188.75575237562</v>
+        <v>1154.907841446441</v>
       </c>
       <c r="U14" t="n">
-        <v>931.994176754212</v>
+        <v>898.146265825033</v>
       </c>
       <c r="V14" t="n">
-        <v>694.7709200200464</v>
+        <v>660.9230090908674</v>
       </c>
       <c r="W14" t="n">
-        <v>448.9391260998974</v>
+        <v>415.0912151707183</v>
       </c>
       <c r="X14" t="n">
-        <v>249.6645468466976</v>
+        <v>215.8166359175186</v>
       </c>
       <c r="Y14" t="n">
-        <v>132.1721906014387</v>
+        <v>98.32427967225962</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1046.845500248624</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="C15" t="n">
-        <v>1046.845500248624</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="D15" t="n">
-        <v>1046.845500248624</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="E15" t="n">
-        <v>700.7120687113384</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="F15" t="n">
-        <v>357.6451572589375</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="G15" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="H15" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I15" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J15" t="n">
-        <v>169.8572291375631</v>
+        <v>169.8572291375641</v>
       </c>
       <c r="K15" t="n">
-        <v>388.277880609305</v>
+        <v>388.277880609306</v>
       </c>
       <c r="L15" t="n">
-        <v>698.9287738082787</v>
+        <v>698.9287738082796</v>
       </c>
       <c r="M15" t="n">
-        <v>830.8710655511379</v>
+        <v>830.8710655511388</v>
       </c>
       <c r="N15" t="n">
-        <v>1011.22692421531</v>
+        <v>1011.226924215311</v>
       </c>
       <c r="O15" t="n">
-        <v>1292.90723383238</v>
+        <v>1292.907233832429</v>
       </c>
       <c r="P15" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="Q15" t="n">
-        <v>1440</v>
+        <v>1288.746311229411</v>
       </c>
       <c r="R15" t="n">
-        <v>1217.678949162759</v>
+        <v>925.1099475930419</v>
       </c>
       <c r="S15" t="n">
-        <v>1148.822374012685</v>
+        <v>856.2533724429675</v>
       </c>
       <c r="T15" t="n">
-        <v>1139.104362643746</v>
+        <v>846.5353610740284</v>
       </c>
       <c r="U15" t="n">
-        <v>1133.853522786877</v>
+        <v>841.2845212171597</v>
       </c>
       <c r="V15" t="n">
-        <v>1114.145778148978</v>
+        <v>477.6481575807928</v>
       </c>
       <c r="W15" t="n">
-        <v>1076.395128745111</v>
+        <v>114.0117939444259</v>
       </c>
       <c r="X15" t="n">
-        <v>1051.281250517447</v>
+        <v>88.89791571676172</v>
       </c>
       <c r="Y15" t="n">
-        <v>1046.845500248624</v>
+        <v>84.46216544793914</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>590.0331199364832</v>
+        <v>947.6008474697212</v>
       </c>
       <c r="C16" t="n">
-        <v>711.085125754919</v>
+        <v>947.6008474697212</v>
       </c>
       <c r="D16" t="n">
-        <v>819.454269879919</v>
+        <v>947.6008474697212</v>
       </c>
       <c r="E16" t="n">
-        <v>932.333174091332</v>
+        <v>947.6008474697212</v>
       </c>
       <c r="F16" t="n">
-        <v>932.333174091332</v>
+        <v>947.6008474697212</v>
       </c>
       <c r="G16" t="n">
-        <v>1080.941485879857</v>
+        <v>1096.209159258246</v>
       </c>
       <c r="H16" t="n">
-        <v>1246.857230055648</v>
+        <v>1096.209159258246</v>
       </c>
       <c r="I16" t="n">
-        <v>1316.955451309033</v>
+        <v>1316.955451309083</v>
       </c>
       <c r="J16" t="n">
-        <v>1316.955451309033</v>
+        <v>1316.955451309083</v>
       </c>
       <c r="K16" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="L16" t="n">
-        <v>1437.626280705164</v>
+        <v>1437.626280705165</v>
       </c>
       <c r="M16" t="n">
-        <v>1334.995492568791</v>
+        <v>1334.995492568793</v>
       </c>
       <c r="N16" t="n">
-        <v>1180.723517215707</v>
+        <v>1180.723517215708</v>
       </c>
       <c r="O16" t="n">
-        <v>954.6827917840143</v>
+        <v>954.6827917840153</v>
       </c>
       <c r="P16" t="n">
-        <v>678.0064921147822</v>
+        <v>678.0064921147832</v>
       </c>
       <c r="Q16" t="n">
-        <v>356.7900613818549</v>
+        <v>356.7900613818559</v>
       </c>
       <c r="R16" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="S16" t="n">
-        <v>63.7447723072879</v>
+        <v>63.74477230728888</v>
       </c>
       <c r="T16" t="n">
-        <v>63.7447723072879</v>
+        <v>63.74477230728888</v>
       </c>
       <c r="U16" t="n">
-        <v>63.7447723072879</v>
+        <v>305.3542419947559</v>
       </c>
       <c r="V16" t="n">
-        <v>63.7447723072879</v>
+        <v>421.3124998405258</v>
       </c>
       <c r="W16" t="n">
-        <v>230.6856905669653</v>
+        <v>588.2534181002032</v>
       </c>
       <c r="X16" t="n">
-        <v>376.7664815911588</v>
+        <v>734.3342091243968</v>
       </c>
       <c r="Y16" t="n">
-        <v>483.2257822701911</v>
+        <v>840.7935098034291</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.17345850496315</v>
+        <v>83.17345850500931</v>
       </c>
       <c r="C17" t="n">
-        <v>37.23954108779758</v>
+        <v>37.23954108784373</v>
       </c>
       <c r="D17" t="n">
-        <v>30.58086303569958</v>
+        <v>30.83635347183385</v>
       </c>
       <c r="E17" t="n">
-        <v>30.21390383684236</v>
+        <v>30.46939427297663</v>
       </c>
       <c r="F17" t="n">
-        <v>29.31528898026473</v>
+        <v>29.570779416399</v>
       </c>
       <c r="G17" t="n">
-        <v>29.31528898026473</v>
+        <v>29.570779416399</v>
       </c>
       <c r="H17" t="n">
-        <v>28.8</v>
+        <v>29.05549043613426</v>
       </c>
       <c r="I17" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J17" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="K17" t="n">
-        <v>71.831941959799</v>
+        <v>71.83194195979998</v>
       </c>
       <c r="L17" t="n">
-        <v>322.4374550181597</v>
+        <v>322.4374550182031</v>
       </c>
       <c r="M17" t="n">
-        <v>678.8374550181611</v>
+        <v>678.8374550182054</v>
       </c>
       <c r="N17" t="n">
-        <v>1035.237455018163</v>
+        <v>1035.237455018208</v>
       </c>
       <c r="O17" t="n">
-        <v>1035.237455018163</v>
+        <v>1035.237455018208</v>
       </c>
       <c r="P17" t="n">
-        <v>1083.599999999999</v>
+        <v>1083.600000000044</v>
       </c>
       <c r="Q17" t="n">
-        <v>1440</v>
+        <v>1440.000000000046</v>
       </c>
       <c r="R17" t="n">
-        <v>1440</v>
+        <v>1440.000000000046</v>
       </c>
       <c r="S17" t="n">
-        <v>1356.099510721982</v>
+        <v>1356.099510722029</v>
       </c>
       <c r="T17" t="n">
-        <v>1173.089659628209</v>
+        <v>1173.089659628256</v>
       </c>
       <c r="U17" t="n">
-        <v>925.4189930977108</v>
+        <v>925.4189930977569</v>
       </c>
       <c r="V17" t="n">
-        <v>697.2866454544543</v>
+        <v>697.2866454545004</v>
       </c>
       <c r="W17" t="n">
-        <v>460.5457606252143</v>
+        <v>460.5457606252605</v>
       </c>
       <c r="X17" t="n">
-        <v>270.3620904629237</v>
+        <v>270.3620904629698</v>
       </c>
       <c r="Y17" t="n">
-        <v>161.9606433085738</v>
+        <v>161.9606433086199</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>691.3848870260487</v>
+        <v>1086.955484076346</v>
       </c>
       <c r="C18" t="n">
-        <v>691.3848870260487</v>
+        <v>723.3191204399803</v>
       </c>
       <c r="D18" t="n">
-        <v>691.3848870260487</v>
+        <v>371.8669114524019</v>
       </c>
       <c r="E18" t="n">
-        <v>691.3848870260487</v>
+        <v>371.8669114524019</v>
       </c>
       <c r="F18" t="n">
-        <v>691.3848870260487</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="G18" t="n">
-        <v>362.5397297671112</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="H18" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I18" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J18" t="n">
-        <v>169.8572291375631</v>
+        <v>169.8572291375641</v>
       </c>
       <c r="K18" t="n">
-        <v>388.277880609305</v>
+        <v>388.277880609306</v>
       </c>
       <c r="L18" t="n">
-        <v>698.9287738082787</v>
+        <v>698.9287738082796</v>
       </c>
       <c r="M18" t="n">
-        <v>830.8710655511379</v>
+        <v>830.8710655511388</v>
       </c>
       <c r="N18" t="n">
-        <v>1010.799828846774</v>
+        <v>1011.226924215311</v>
       </c>
       <c r="O18" t="n">
-        <v>1292.90723383238</v>
+        <v>1292.907233832426</v>
       </c>
       <c r="P18" t="n">
-        <v>1440</v>
+        <v>1440.000000000046</v>
       </c>
       <c r="Q18" t="n">
-        <v>1440</v>
+        <v>1440.000000000046</v>
       </c>
       <c r="R18" t="n">
-        <v>1306.745163779377</v>
+        <v>1306.745163779423</v>
       </c>
       <c r="S18" t="n">
-        <v>1246.979497720212</v>
+        <v>1246.979497720258</v>
       </c>
       <c r="T18" t="n">
-        <v>1246.352395442182</v>
+        <v>1246.352395442228</v>
       </c>
       <c r="U18" t="n">
-        <v>1246.352395442182</v>
+        <v>1246.352395442228</v>
       </c>
       <c r="V18" t="n">
-        <v>1071.044219799169</v>
+        <v>1235.735559895238</v>
       </c>
       <c r="W18" t="n">
-        <v>707.4078561628038</v>
+        <v>1207.07581958228</v>
       </c>
       <c r="X18" t="n">
-        <v>691.3848870260487</v>
+        <v>1191.052850445524</v>
       </c>
       <c r="Y18" t="n">
-        <v>691.3848870260487</v>
+        <v>1086.955484076346</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>320.3682559259695</v>
+        <v>1010.207938817935</v>
       </c>
       <c r="C19" t="n">
-        <v>450.3302617444053</v>
+        <v>1140.169944636371</v>
       </c>
       <c r="D19" t="n">
-        <v>567.6094058694055</v>
+        <v>1257.449088761371</v>
       </c>
       <c r="E19" t="n">
-        <v>567.6094058694055</v>
+        <v>1379.237992972784</v>
       </c>
       <c r="F19" t="n">
-        <v>695.930378461341</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="G19" t="n">
-        <v>695.930378461341</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="H19" t="n">
-        <v>695.930378461341</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="I19" t="n">
-        <v>925.586670512178</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="J19" t="n">
-        <v>1251.126277468743</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="K19" t="n">
-        <v>1383.080826159709</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="L19" t="n">
-        <v>1383.080826159709</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="M19" t="n">
-        <v>1289.540947114246</v>
+        <v>1289.540947114247</v>
       </c>
       <c r="N19" t="n">
-        <v>1144.35988085207</v>
+        <v>1144.359880852071</v>
       </c>
       <c r="O19" t="n">
-        <v>927.4100645112869</v>
+        <v>927.4100645112879</v>
       </c>
       <c r="P19" t="n">
-        <v>659.8246739329639</v>
+        <v>659.824673932965</v>
       </c>
       <c r="Q19" t="n">
-        <v>347.6991522909458</v>
+        <v>347.6991522909468</v>
       </c>
       <c r="R19" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="S19" t="n">
-        <v>28.8</v>
+        <v>72.65477230728888</v>
       </c>
       <c r="T19" t="n">
-        <v>28.8</v>
+        <v>265.3388203185527</v>
       </c>
       <c r="U19" t="n">
-        <v>28.8</v>
+        <v>515.8582900060197</v>
       </c>
       <c r="V19" t="n">
-        <v>28.8</v>
+        <v>718.6396828919657</v>
       </c>
       <c r="W19" t="n">
-        <v>204.6509182596774</v>
+        <v>894.4906011516431</v>
       </c>
       <c r="X19" t="n">
-        <v>204.6509182596774</v>
+        <v>894.4906011516431</v>
       </c>
       <c r="Y19" t="n">
-        <v>204.6509182596774</v>
+        <v>894.4906011516431</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82.91796806887504</v>
+        <v>83.17345850501022</v>
       </c>
       <c r="C20" t="n">
-        <v>36.98405065170947</v>
+        <v>37.23954108784464</v>
       </c>
       <c r="D20" t="n">
-        <v>30.58086303569958</v>
+        <v>30.83635347183476</v>
       </c>
       <c r="E20" t="n">
-        <v>30.21390383684236</v>
+        <v>30.21390383684335</v>
       </c>
       <c r="F20" t="n">
-        <v>29.31528898026473</v>
+        <v>29.31528898026572</v>
       </c>
       <c r="G20" t="n">
-        <v>29.31528898026473</v>
+        <v>29.31528898026572</v>
       </c>
       <c r="H20" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I20" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J20" t="n">
-        <v>385.2000000000015</v>
+        <v>385.2000000000034</v>
       </c>
       <c r="K20" t="n">
-        <v>428.2319419598006</v>
+        <v>741.6000000000156</v>
       </c>
       <c r="L20" t="n">
-        <v>481.6168711055292</v>
+        <v>794.9849291457442</v>
       </c>
       <c r="M20" t="n">
-        <v>838.0168711055308</v>
+        <v>1151.384929145747</v>
       </c>
       <c r="N20" t="n">
-        <v>1194.416871105532</v>
+        <v>1391.637455018211</v>
       </c>
       <c r="O20" t="n">
-        <v>1194.416871105532</v>
+        <v>1391.637455018211</v>
       </c>
       <c r="P20" t="n">
-        <v>1242.779416087368</v>
+        <v>1440.000000000047</v>
       </c>
       <c r="Q20" t="n">
-        <v>1440</v>
+        <v>1440.000000000047</v>
       </c>
       <c r="R20" t="n">
-        <v>1439.744509563912</v>
+        <v>1440.000000000047</v>
       </c>
       <c r="S20" t="n">
-        <v>1355.844020285894</v>
+        <v>1356.099510722029</v>
       </c>
       <c r="T20" t="n">
-        <v>1172.834169192121</v>
+        <v>1173.089659628256</v>
       </c>
       <c r="U20" t="n">
-        <v>925.1635026616227</v>
+        <v>925.4189930977578</v>
       </c>
       <c r="V20" t="n">
-        <v>697.0311550183662</v>
+        <v>697.2866454545014</v>
       </c>
       <c r="W20" t="n">
-        <v>460.2902701891262</v>
+        <v>460.5457606252614</v>
       </c>
       <c r="X20" t="n">
-        <v>270.1066000268356</v>
+        <v>270.3620904629707</v>
       </c>
       <c r="Y20" t="n">
-        <v>161.7051528724857</v>
+        <v>161.9606433086208</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>743.8885726239437</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="C21" t="n">
-        <v>380.2522089875785</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="D21" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="E21" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="F21" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="G21" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="H21" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I21" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J21" t="n">
-        <v>169.8572291375631</v>
+        <v>169.8572291375641</v>
       </c>
       <c r="K21" t="n">
-        <v>388.277880609305</v>
+        <v>388.277880609306</v>
       </c>
       <c r="L21" t="n">
-        <v>698.9287738082787</v>
+        <v>698.9287738082796</v>
       </c>
       <c r="M21" t="n">
-        <v>830.8710655511379</v>
+        <v>830.8710655511388</v>
       </c>
       <c r="N21" t="n">
-        <v>1011.22692421531</v>
+        <v>1011.226924215311</v>
       </c>
       <c r="O21" t="n">
-        <v>1292.90723383238</v>
+        <v>1292.907233832429</v>
       </c>
       <c r="P21" t="n">
-        <v>1440</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="Q21" t="n">
-        <v>1288.746311229361</v>
+        <v>1288.746311229411</v>
       </c>
       <c r="R21" t="n">
-        <v>1155.491475008738</v>
+        <v>1155.491475008787</v>
       </c>
       <c r="S21" t="n">
-        <v>1095.725808949573</v>
+        <v>1095.725808949622</v>
       </c>
       <c r="T21" t="n">
-        <v>1095.098706671543</v>
+        <v>1095.098706671592</v>
       </c>
       <c r="U21" t="n">
-        <v>1095.098706671543</v>
+        <v>1095.098706671592</v>
       </c>
       <c r="V21" t="n">
-        <v>1084.481871124553</v>
+        <v>731.4623430352261</v>
       </c>
       <c r="W21" t="n">
-        <v>1055.822130811595</v>
+        <v>392.4363636363671</v>
       </c>
       <c r="X21" t="n">
-        <v>1039.79916167484</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="Y21" t="n">
-        <v>1039.79916167484</v>
+        <v>28.80000000000099</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>438.6764543371752</v>
+        <v>800.6268933920463</v>
       </c>
       <c r="C22" t="n">
-        <v>568.638460155611</v>
+        <v>800.6268933920463</v>
       </c>
       <c r="D22" t="n">
-        <v>685.9176042806112</v>
+        <v>800.6268933920463</v>
       </c>
       <c r="E22" t="n">
-        <v>685.9176042806112</v>
+        <v>922.4157976034594</v>
       </c>
       <c r="F22" t="n">
-        <v>685.9176042806112</v>
+        <v>1050.736770195395</v>
       </c>
       <c r="G22" t="n">
-        <v>843.4359160691358</v>
+        <v>1208.25508198392</v>
       </c>
       <c r="H22" t="n">
-        <v>1018.261660244927</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="I22" t="n">
-        <v>1247.917952295764</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="J22" t="n">
-        <v>1247.917952295764</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="K22" t="n">
-        <v>1379.872500986731</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="L22" t="n">
-        <v>1383.080826159709</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="M22" t="n">
-        <v>1289.540947114246</v>
+        <v>1289.540947114247</v>
       </c>
       <c r="N22" t="n">
-        <v>1144.35988085207</v>
+        <v>1144.359880852071</v>
       </c>
       <c r="O22" t="n">
-        <v>927.4100645112869</v>
+        <v>927.4100645112879</v>
       </c>
       <c r="P22" t="n">
-        <v>659.8246739329639</v>
+        <v>659.824673932965</v>
       </c>
       <c r="Q22" t="n">
-        <v>347.6991522909458</v>
+        <v>347.6991522909468</v>
       </c>
       <c r="R22" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="S22" t="n">
-        <v>72.6547723072879</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="T22" t="n">
-        <v>168.3163626339494</v>
+        <v>35.91715287690511</v>
       </c>
       <c r="U22" t="n">
-        <v>168.3163626339494</v>
+        <v>35.91715287690511</v>
       </c>
       <c r="V22" t="n">
-        <v>168.3163626339494</v>
+        <v>238.6985457628511</v>
       </c>
       <c r="W22" t="n">
-        <v>168.3163626339494</v>
+        <v>414.5494640225285</v>
       </c>
       <c r="X22" t="n">
-        <v>323.307153658143</v>
+        <v>569.540255046722</v>
       </c>
       <c r="Y22" t="n">
-        <v>438.6764543371752</v>
+        <v>684.9095557257542</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82.91796806887504</v>
+        <v>82.91796806887604</v>
       </c>
       <c r="C23" t="n">
-        <v>36.98405065170947</v>
+        <v>36.98405065171045</v>
       </c>
       <c r="D23" t="n">
-        <v>30.58086303569958</v>
+        <v>30.58086303570057</v>
       </c>
       <c r="E23" t="n">
-        <v>30.21390383684236</v>
+        <v>30.21390383684335</v>
       </c>
       <c r="F23" t="n">
-        <v>29.31528898026473</v>
+        <v>29.31528898026572</v>
       </c>
       <c r="G23" t="n">
-        <v>29.31528898026473</v>
+        <v>29.31528898026572</v>
       </c>
       <c r="H23" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I23" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J23" t="n">
-        <v>28.8</v>
+        <v>385.200000000004</v>
       </c>
       <c r="K23" t="n">
-        <v>71.831941959799</v>
+        <v>741.6000000000162</v>
       </c>
       <c r="L23" t="n">
-        <v>125.2168711055276</v>
+        <v>794.9849291457448</v>
       </c>
       <c r="M23" t="n">
-        <v>370.7999999999945</v>
+        <v>794.9849291457448</v>
       </c>
       <c r="N23" t="n">
-        <v>370.7999999999945</v>
+        <v>1035.237455018206</v>
       </c>
       <c r="O23" t="n">
-        <v>727.1999999999963</v>
+        <v>1035.237455018206</v>
       </c>
       <c r="P23" t="n">
-        <v>1083.599999999998</v>
+        <v>1083.600000000042</v>
       </c>
       <c r="Q23" t="n">
-        <v>1440</v>
+        <v>1440.000000000045</v>
       </c>
       <c r="R23" t="n">
-        <v>1439.744509563912</v>
+        <v>1439.744509563913</v>
       </c>
       <c r="S23" t="n">
-        <v>1355.844020285894</v>
+        <v>1355.844020285895</v>
       </c>
       <c r="T23" t="n">
-        <v>1172.834169192121</v>
+        <v>1172.834169192122</v>
       </c>
       <c r="U23" t="n">
-        <v>925.1635026616227</v>
+        <v>925.1635026616236</v>
       </c>
       <c r="V23" t="n">
-        <v>697.0311550183662</v>
+        <v>697.0311550183671</v>
       </c>
       <c r="W23" t="n">
-        <v>460.2902701891262</v>
+        <v>460.2902701891272</v>
       </c>
       <c r="X23" t="n">
-        <v>270.1066000268356</v>
+        <v>270.1066000268365</v>
       </c>
       <c r="Y23" t="n">
-        <v>161.7051528724857</v>
+        <v>161.7051528724867</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1039.799161674892</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="C24" t="n">
-        <v>726.3856405248639</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="D24" t="n">
-        <v>374.9334315372855</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="E24" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="F24" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="G24" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="H24" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="I24" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="J24" t="n">
-        <v>169.8572291375631</v>
+        <v>169.8572291375641</v>
       </c>
       <c r="K24" t="n">
-        <v>388.277880609305</v>
+        <v>388.277880609306</v>
       </c>
       <c r="L24" t="n">
-        <v>698.9287738082787</v>
+        <v>698.9287738082796</v>
       </c>
       <c r="M24" t="n">
-        <v>830.8710655511379</v>
+        <v>830.8710655511388</v>
       </c>
       <c r="N24" t="n">
-        <v>1011.22692421531</v>
+        <v>1011.226924215311</v>
       </c>
       <c r="O24" t="n">
-        <v>1292.907233832433</v>
+        <v>1292.907233832425</v>
       </c>
       <c r="P24" t="n">
-        <v>1440.000000000053</v>
+        <v>1440.000000000045</v>
       </c>
       <c r="Q24" t="n">
-        <v>1288.746311229414</v>
+        <v>1440.000000000049</v>
       </c>
       <c r="R24" t="n">
-        <v>1155.491475008791</v>
+        <v>1306.745163779426</v>
       </c>
       <c r="S24" t="n">
-        <v>1095.725808949626</v>
+        <v>1246.979497720261</v>
       </c>
       <c r="T24" t="n">
-        <v>1095.098706671596</v>
+        <v>1246.352395442231</v>
       </c>
       <c r="U24" t="n">
-        <v>1095.098706671596</v>
+        <v>1119.709090909101</v>
       </c>
       <c r="V24" t="n">
-        <v>1084.481871124606</v>
+        <v>756.0727272727345</v>
       </c>
       <c r="W24" t="n">
-        <v>1055.822130811647</v>
+        <v>392.4363636363677</v>
       </c>
       <c r="X24" t="n">
-        <v>1039.799161674892</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="Y24" t="n">
-        <v>1039.799161674892</v>
+        <v>28.80000000000099</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030.048560833693</v>
+        <v>227.6455633314824</v>
       </c>
       <c r="C25" t="n">
-        <v>1160.010566652129</v>
+        <v>227.6455633314824</v>
       </c>
       <c r="D25" t="n">
-        <v>1160.010566652129</v>
+        <v>227.6455633314824</v>
       </c>
       <c r="E25" t="n">
-        <v>1160.010566652129</v>
+        <v>349.4344675428954</v>
       </c>
       <c r="F25" t="n">
-        <v>1160.010566652129</v>
+        <v>349.4344675428954</v>
       </c>
       <c r="G25" t="n">
-        <v>1160.010566652129</v>
+        <v>506.95277933142</v>
       </c>
       <c r="H25" t="n">
-        <v>1334.83631082792</v>
+        <v>681.778523507211</v>
       </c>
       <c r="I25" t="n">
-        <v>1383.08082615971</v>
+        <v>911.4348155580481</v>
       </c>
       <c r="J25" t="n">
-        <v>1383.08082615971</v>
+        <v>1247.917952295765</v>
       </c>
       <c r="K25" t="n">
-        <v>1383.08082615971</v>
+        <v>1379.872500986732</v>
       </c>
       <c r="L25" t="n">
-        <v>1383.08082615971</v>
+        <v>1383.080826159711</v>
       </c>
       <c r="M25" t="n">
-        <v>1289.540947114246</v>
+        <v>1289.540947114247</v>
       </c>
       <c r="N25" t="n">
         <v>1144.359880852071</v>
       </c>
       <c r="O25" t="n">
-        <v>927.4100645112871</v>
+        <v>927.4100645112881</v>
       </c>
       <c r="P25" t="n">
-        <v>659.8246739329641</v>
+        <v>659.824673932965</v>
       </c>
       <c r="Q25" t="n">
-        <v>347.6991522909458</v>
+        <v>347.6991522909468</v>
       </c>
       <c r="R25" t="n">
-        <v>28.8</v>
+        <v>28.80000000000099</v>
       </c>
       <c r="S25" t="n">
-        <v>72.65477230728787</v>
+        <v>72.65477230728885</v>
       </c>
       <c r="T25" t="n">
-        <v>265.3388203185518</v>
+        <v>72.65477230728885</v>
       </c>
       <c r="U25" t="n">
-        <v>265.3388203185518</v>
+        <v>72.65477230728885</v>
       </c>
       <c r="V25" t="n">
-        <v>468.1202132044978</v>
+        <v>72.65477230728885</v>
       </c>
       <c r="W25" t="n">
-        <v>643.9711314641752</v>
+        <v>72.65477230728885</v>
       </c>
       <c r="X25" t="n">
-        <v>798.9619224883687</v>
+        <v>227.6455633314824</v>
       </c>
       <c r="Y25" t="n">
-        <v>914.3312231674009</v>
+        <v>227.6455633314824</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>306.3355106814288</v>
+        <v>179.4182902063409</v>
       </c>
       <c r="C26" t="n">
-        <v>306.3355106814288</v>
+        <v>179.4182902063409</v>
       </c>
       <c r="D26" t="n">
-        <v>209.023232156328</v>
+        <v>179.4182902063409</v>
       </c>
       <c r="E26" t="n">
-        <v>209.023232156328</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="F26" t="n">
-        <v>209.023232156328</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="G26" t="n">
-        <v>118.7043798893556</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="H26" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="I26" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="J26" t="n">
-        <v>364.87</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="K26" t="n">
-        <v>407.901941959799</v>
+        <v>70.31194195979998</v>
       </c>
       <c r="L26" t="n">
-        <v>461.2868711055277</v>
+        <v>302.8674550181768</v>
       </c>
       <c r="M26" t="n">
-        <v>640.4574550181642</v>
+        <v>640.457455018189</v>
       </c>
       <c r="N26" t="n">
-        <v>978.0474550181641</v>
+        <v>978.0474550182012</v>
       </c>
       <c r="O26" t="n">
-        <v>978.0474550181641</v>
+        <v>978.0474550182012</v>
       </c>
       <c r="P26" t="n">
-        <v>1026.41</v>
+        <v>1026.410000000037</v>
       </c>
       <c r="Q26" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="R26" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="S26" t="n">
-        <v>1189.190419812891</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="T26" t="n">
-        <v>1189.190419812891</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="U26" t="n">
-        <v>1084.774523203843</v>
+        <v>1025.42024256046</v>
       </c>
       <c r="V26" t="n">
-        <v>1084.774523203843</v>
+        <v>706.3788040081125</v>
       </c>
       <c r="W26" t="n">
-        <v>757.1245474655119</v>
+        <v>378.7288282697817</v>
       </c>
       <c r="X26" t="n">
-        <v>476.0317863941303</v>
+        <v>378.7288282697817</v>
       </c>
       <c r="Y26" t="n">
-        <v>476.0317863941303</v>
+        <v>179.4182902063409</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>325.0061020911743</v>
+        <v>192.2345222816167</v>
       </c>
       <c r="C27" t="n">
-        <v>277.4304329542862</v>
+        <v>144.6588531447285</v>
       </c>
       <c r="D27" t="n">
-        <v>110.3783613288663</v>
+        <v>110.3783613288673</v>
       </c>
       <c r="E27" t="n">
-        <v>81.41664696329795</v>
+        <v>81.41664696329894</v>
       </c>
       <c r="F27" t="n">
-        <v>55.52145268261424</v>
+        <v>55.52145268261523</v>
       </c>
       <c r="G27" t="n">
-        <v>43.84801259539394</v>
+        <v>43.84801259539493</v>
       </c>
       <c r="H27" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="I27" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="J27" t="n">
-        <v>168.3372291375631</v>
+        <v>168.3372291375641</v>
       </c>
       <c r="K27" t="n">
-        <v>386.7578806093051</v>
+        <v>386.757880609306</v>
       </c>
       <c r="L27" t="n">
-        <v>697.4087738082787</v>
+        <v>697.4087738082796</v>
       </c>
       <c r="M27" t="n">
-        <v>754.4439701826024</v>
+        <v>829.3510655511388</v>
       </c>
       <c r="N27" t="n">
-        <v>934.7998288467744</v>
+        <v>1009.706924215311</v>
       </c>
       <c r="O27" t="n">
-        <v>1216.90723383238</v>
+        <v>1291.814329200917</v>
       </c>
       <c r="P27" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="Q27" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="R27" t="n">
-        <v>1139.836072870286</v>
+        <v>1139.836072870335</v>
       </c>
       <c r="S27" t="n">
-        <v>989.1613159020296</v>
+        <v>856.389736092472</v>
       </c>
       <c r="T27" t="n">
-        <v>897.6251227149087</v>
+        <v>764.8535429053511</v>
       </c>
       <c r="U27" t="n">
-        <v>810.5561010398583</v>
+        <v>677.7845212303007</v>
       </c>
       <c r="V27" t="n">
-        <v>709.0301745837774</v>
+        <v>576.2585947742198</v>
       </c>
       <c r="W27" t="n">
-        <v>589.4613433617284</v>
+        <v>456.6897635521707</v>
       </c>
       <c r="X27" t="n">
-        <v>482.5292833158824</v>
+        <v>349.7577035063247</v>
       </c>
       <c r="Y27" t="n">
-        <v>396.275351228878</v>
+        <v>263.5037714193203</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>598.8219006487433</v>
+        <v>598.8219006487924</v>
       </c>
       <c r="C28" t="n">
-        <v>639.6839064671791</v>
+        <v>639.6839064672282</v>
       </c>
       <c r="D28" t="n">
-        <v>667.8630505921792</v>
+        <v>667.8630505922283</v>
       </c>
       <c r="E28" t="n">
-        <v>700.5519548035923</v>
+        <v>700.5519548036414</v>
       </c>
       <c r="F28" t="n">
-        <v>739.7729273955277</v>
+        <v>739.7729273955769</v>
       </c>
       <c r="G28" t="n">
-        <v>808.1912391840524</v>
+        <v>808.1912391841015</v>
       </c>
       <c r="H28" t="n">
-        <v>893.9169833598434</v>
+        <v>893.9169833598925</v>
       </c>
       <c r="I28" t="n">
-        <v>1034.47327541068</v>
+        <v>1034.473275410729</v>
       </c>
       <c r="J28" t="n">
-        <v>1321.145451309033</v>
+        <v>1321.145451309083</v>
       </c>
       <c r="K28" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="L28" t="n">
-        <v>1364</v>
+        <v>1276.364376260613</v>
       </c>
       <c r="M28" t="n">
-        <v>1179.551030045445</v>
+        <v>1091.915406306059</v>
       </c>
       <c r="N28" t="n">
-        <v>943.460872874179</v>
+        <v>855.8252491347924</v>
       </c>
       <c r="O28" t="n">
-        <v>635.6019656243047</v>
+        <v>855.8252491347924</v>
       </c>
       <c r="P28" t="n">
-        <v>291.1575211798603</v>
+        <v>762.3327779744286</v>
       </c>
       <c r="Q28" t="n">
-        <v>291.1575211798603</v>
+        <v>417.8883335299718</v>
       </c>
       <c r="R28" t="n">
-        <v>27.28</v>
+        <v>73.44388908551485</v>
       </c>
       <c r="S28" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="T28" t="n">
-        <v>130.8640480112639</v>
+        <v>130.8640480112649</v>
       </c>
       <c r="U28" t="n">
-        <v>279.612160133602</v>
+        <v>279.6121601336511</v>
       </c>
       <c r="V28" t="n">
-        <v>393.293553019548</v>
+        <v>393.2935530195971</v>
       </c>
       <c r="W28" t="n">
-        <v>480.0444712792254</v>
+        <v>480.0444712792745</v>
       </c>
       <c r="X28" t="n">
-        <v>545.9352623034189</v>
+        <v>545.935262303468</v>
       </c>
       <c r="Y28" t="n">
-        <v>572.2045629824512</v>
+        <v>572.2045629825003</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="C29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="D29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="E29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="F29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="G29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="H29" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="I29" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="J29" t="n">
-        <v>364.87</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="K29" t="n">
-        <v>702.46</v>
+        <v>70.31194195979998</v>
       </c>
       <c r="L29" t="n">
-        <v>755.8449291457287</v>
+        <v>302.8674550181768</v>
       </c>
       <c r="M29" t="n">
-        <v>978.0474550181641</v>
+        <v>640.457455018189</v>
       </c>
       <c r="N29" t="n">
-        <v>1315.637455018164</v>
+        <v>978.0474550182012</v>
       </c>
       <c r="O29" t="n">
-        <v>1315.637455018164</v>
+        <v>978.0474550182012</v>
       </c>
       <c r="P29" t="n">
-        <v>1364</v>
+        <v>1026.410000000037</v>
       </c>
       <c r="Q29" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="R29" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="S29" t="n">
-        <v>1189.190419812891</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="T29" t="n">
-        <v>915.2714778100275</v>
+        <v>1103.975551619624</v>
       </c>
       <c r="U29" t="n">
-        <v>576.691720370438</v>
+        <v>765.3957941800348</v>
       </c>
       <c r="V29" t="n">
-        <v>257.6502818180907</v>
+        <v>446.3543556276875</v>
       </c>
       <c r="W29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="X29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
       <c r="Y29" t="n">
-        <v>27.28</v>
+        <v>118.7043798893566</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>325.0061020911743</v>
+        <v>325.0061020912237</v>
       </c>
       <c r="C30" t="n">
-        <v>277.4304329542862</v>
+        <v>277.4304329543355</v>
       </c>
       <c r="D30" t="n">
-        <v>243.1499411384249</v>
+        <v>243.1499411384743</v>
       </c>
       <c r="E30" t="n">
-        <v>214.1882267728566</v>
+        <v>214.188226772906</v>
       </c>
       <c r="F30" t="n">
-        <v>188.2930324921729</v>
+        <v>188.2930324922223</v>
       </c>
       <c r="G30" t="n">
-        <v>176.6195924049526</v>
+        <v>176.619592405002</v>
       </c>
       <c r="H30" t="n">
-        <v>160.0515798095587</v>
+        <v>160.051579809608</v>
       </c>
       <c r="I30" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="J30" t="n">
-        <v>168.3372291375631</v>
+        <v>168.3372291375641</v>
       </c>
       <c r="K30" t="n">
-        <v>386.7578806093051</v>
+        <v>386.757880609306</v>
       </c>
       <c r="L30" t="n">
-        <v>697.4087738082787</v>
+        <v>697.4087738082796</v>
       </c>
       <c r="M30" t="n">
-        <v>829.3510655511379</v>
+        <v>829.3510655511388</v>
       </c>
       <c r="N30" t="n">
-        <v>1009.70692421531</v>
+        <v>1009.706924215311</v>
       </c>
       <c r="O30" t="n">
-        <v>1291.814329200916</v>
+        <v>1291.814329200917</v>
       </c>
       <c r="P30" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="Q30" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="R30" t="n">
-        <v>1139.836072870286</v>
+        <v>1139.836072870335</v>
       </c>
       <c r="S30" t="n">
-        <v>989.1613159020296</v>
+        <v>989.161315902079</v>
       </c>
       <c r="T30" t="n">
-        <v>897.6251227149087</v>
+        <v>897.625122714958</v>
       </c>
       <c r="U30" t="n">
-        <v>810.5561010398583</v>
+        <v>810.5561010399076</v>
       </c>
       <c r="V30" t="n">
-        <v>709.0301745837774</v>
+        <v>709.0301745838267</v>
       </c>
       <c r="W30" t="n">
-        <v>589.4613433617284</v>
+        <v>589.4613433617777</v>
       </c>
       <c r="X30" t="n">
-        <v>482.5292833158824</v>
+        <v>482.5292833159317</v>
       </c>
       <c r="Y30" t="n">
-        <v>396.275351228878</v>
+        <v>396.2753512289273</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>598.8219006487433</v>
+        <v>611.4932582138731</v>
       </c>
       <c r="C31" t="n">
-        <v>639.6839064671791</v>
+        <v>652.3552640323089</v>
       </c>
       <c r="D31" t="n">
-        <v>667.8630505921792</v>
+        <v>680.534408157309</v>
       </c>
       <c r="E31" t="n">
-        <v>700.5519548035923</v>
+        <v>713.2233123687221</v>
       </c>
       <c r="F31" t="n">
-        <v>739.7729273955277</v>
+        <v>752.4442849606576</v>
       </c>
       <c r="G31" t="n">
-        <v>808.1912391840524</v>
+        <v>808.1912391841015</v>
       </c>
       <c r="H31" t="n">
-        <v>893.9169833598434</v>
+        <v>893.9169833598925</v>
       </c>
       <c r="I31" t="n">
-        <v>1034.47327541068</v>
+        <v>1034.473275410729</v>
       </c>
       <c r="J31" t="n">
-        <v>1321.145451309033</v>
+        <v>1321.145451309083</v>
       </c>
       <c r="K31" t="n">
-        <v>1364</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="L31" t="n">
-        <v>1276.364376260564</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="M31" t="n">
-        <v>1091.91540630601</v>
+        <v>1364.000000000049</v>
       </c>
       <c r="N31" t="n">
-        <v>855.8252491347431</v>
+        <v>1127.909842828783</v>
       </c>
       <c r="O31" t="n">
-        <v>547.9663418848688</v>
+        <v>820.0509355789086</v>
       </c>
       <c r="P31" t="n">
-        <v>547.9663418848688</v>
+        <v>475.6064911344517</v>
       </c>
       <c r="Q31" t="n">
-        <v>417.8883335299583</v>
+        <v>131.1620466899948</v>
       </c>
       <c r="R31" t="n">
-        <v>73.44388908551386</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="S31" t="n">
-        <v>27.28</v>
+        <v>27.28000000000099</v>
       </c>
       <c r="T31" t="n">
-        <v>130.8640480112639</v>
+        <v>130.8640480112649</v>
       </c>
       <c r="U31" t="n">
-        <v>279.612160133602</v>
+        <v>292.2835176987318</v>
       </c>
       <c r="V31" t="n">
-        <v>393.293553019548</v>
+        <v>405.9649105846778</v>
       </c>
       <c r="W31" t="n">
-        <v>480.0444712792254</v>
+        <v>492.7158288443552</v>
       </c>
       <c r="X31" t="n">
-        <v>545.9352623034189</v>
+        <v>558.6066198685487</v>
       </c>
       <c r="Y31" t="n">
-        <v>572.2045629824512</v>
+        <v>584.875920547581</v>
       </c>
     </row>
     <row r="32">
@@ -6697,19 +6697,19 @@
         <v>69.27194195979899</v>
       </c>
       <c r="L32" t="n">
-        <v>122.6568711055276</v>
+        <v>289.477455018164</v>
       </c>
       <c r="M32" t="n">
-        <v>447.3768711055291</v>
+        <v>614.197455018164</v>
       </c>
       <c r="N32" t="n">
-        <v>772.0968711055305</v>
+        <v>938.917455018164</v>
       </c>
       <c r="O32" t="n">
-        <v>1096.816871105532</v>
+        <v>938.917455018164</v>
       </c>
       <c r="P32" t="n">
-        <v>1145.179416087368</v>
+        <v>987.28</v>
       </c>
       <c r="Q32" t="n">
         <v>1312</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>104.6441371804623</v>
+        <v>26.24</v>
       </c>
       <c r="C33" t="n">
         <v>26.24</v>
@@ -6776,13 +6776,13 @@
         <v>385.717880609305</v>
       </c>
       <c r="L33" t="n">
-        <v>570.5016784397432</v>
+        <v>696.3687738082788</v>
       </c>
       <c r="M33" t="n">
-        <v>702.4439701826024</v>
+        <v>828.311065551138</v>
       </c>
       <c r="N33" t="n">
-        <v>882.7998288467744</v>
+        <v>1008.66692421531</v>
       </c>
       <c r="O33" t="n">
         <v>1164.90723383238</v>
@@ -6794,28 +6794,28 @@
         <v>1160.746311229361</v>
       </c>
       <c r="R33" t="n">
-        <v>829.4331799162248</v>
+        <v>1040.622788140051</v>
       </c>
       <c r="S33" t="n">
-        <v>782.7988269883728</v>
+        <v>993.9884352121991</v>
       </c>
       <c r="T33" t="n">
-        <v>782.7988269883728</v>
+        <v>993.9884352121991</v>
       </c>
       <c r="U33" t="n">
-        <v>782.7988269883728</v>
+        <v>662.6753038990678</v>
       </c>
       <c r="V33" t="n">
-        <v>782.7988269883728</v>
+        <v>331.3621725859364</v>
       </c>
       <c r="W33" t="n">
-        <v>767.2703998067278</v>
+        <v>29.13165600544197</v>
       </c>
       <c r="X33" t="n">
-        <v>435.9572684935951</v>
+        <v>26.24</v>
       </c>
       <c r="Y33" t="n">
-        <v>104.6441371804623</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="34">
@@ -6825,31 +6825,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>855.4947587799577</v>
+        <v>575.6847415762421</v>
       </c>
       <c r="C34" t="n">
-        <v>855.4947587799577</v>
+        <v>718.5167473946779</v>
       </c>
       <c r="D34" t="n">
-        <v>855.4947587799577</v>
+        <v>848.6658915196779</v>
       </c>
       <c r="E34" t="n">
-        <v>990.1536629913707</v>
+        <v>983.3247957310909</v>
       </c>
       <c r="F34" t="n">
-        <v>1131.344635583306</v>
+        <v>986.5200868923394</v>
       </c>
       <c r="G34" t="n">
-        <v>1301.732947371831</v>
+        <v>1156.908398680864</v>
       </c>
       <c r="H34" t="n">
-        <v>1301.732947371831</v>
+        <v>1156.908398680864</v>
       </c>
       <c r="I34" t="n">
-        <v>1301.732947371831</v>
+        <v>1156.908398680864</v>
       </c>
       <c r="J34" t="n">
-        <v>1301.732947371831</v>
+        <v>1156.908398680864</v>
       </c>
       <c r="K34" t="n">
         <v>1301.732947371831</v>
@@ -6879,22 +6879,22 @@
         <v>26.24</v>
       </c>
       <c r="T34" t="n">
-        <v>26.24</v>
+        <v>231.7940480112639</v>
       </c>
       <c r="U34" t="n">
-        <v>242.0864111507624</v>
+        <v>231.7940480112639</v>
       </c>
       <c r="V34" t="n">
-        <v>242.0864111507624</v>
+        <v>447.4454408972099</v>
       </c>
       <c r="W34" t="n">
-        <v>430.8073294104398</v>
+        <v>447.4454408972099</v>
       </c>
       <c r="X34" t="n">
-        <v>598.6681204346334</v>
+        <v>447.4454408972099</v>
       </c>
       <c r="Y34" t="n">
-        <v>726.9074211136656</v>
+        <v>575.6847415762421</v>
       </c>
     </row>
     <row r="35">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>57.79250327575143</v>
+        <v>56.3047716362762</v>
       </c>
       <c r="C35" t="n">
         <v>26</v>
@@ -6931,22 +6931,22 @@
         <v>26</v>
       </c>
       <c r="K35" t="n">
-        <v>69.031941959799</v>
+        <v>347.75</v>
       </c>
       <c r="L35" t="n">
-        <v>390.781941959799</v>
+        <v>401.1349291457287</v>
       </c>
       <c r="M35" t="n">
-        <v>712.531941959799</v>
+        <v>722.8849291457286</v>
       </c>
       <c r="N35" t="n">
-        <v>1034.281941959799</v>
+        <v>1044.634929145729</v>
       </c>
       <c r="O35" t="n">
-        <v>1034.281941959799</v>
+        <v>1044.634929145729</v>
       </c>
       <c r="P35" t="n">
-        <v>1082.644486941635</v>
+        <v>1092.997474127565</v>
       </c>
       <c r="Q35" t="n">
         <v>1300</v>
@@ -6955,25 +6955,25 @@
         <v>1300</v>
       </c>
       <c r="S35" t="n">
-        <v>1231.728656502872</v>
+        <v>1230.240924863396</v>
       </c>
       <c r="T35" t="n">
-        <v>1062.860219550513</v>
+        <v>1061.372487911038</v>
       </c>
       <c r="U35" t="n">
-        <v>829.3309671614284</v>
+        <v>827.843235521953</v>
       </c>
       <c r="V35" t="n">
-        <v>615.340033659586</v>
+        <v>613.8523020201108</v>
       </c>
       <c r="W35" t="n">
-        <v>392.7405629717601</v>
+        <v>391.2528313322849</v>
       </c>
       <c r="X35" t="n">
-        <v>216.6983069508836</v>
+        <v>215.2105753114084</v>
       </c>
       <c r="Y35" t="n">
-        <v>122.4382739379479</v>
+        <v>120.9505422984727</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>354.2828282828283</v>
+        <v>682.5656565656566</v>
       </c>
       <c r="C36" t="n">
         <v>354.2828282828283</v>
       </c>
       <c r="D36" t="n">
-        <v>354.2828282828283</v>
+        <v>26</v>
       </c>
       <c r="E36" t="n">
-        <v>354.2828282828283</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
         <v>26</v>
@@ -7019,10 +7019,10 @@
         <v>828.071065551138</v>
       </c>
       <c r="N36" t="n">
-        <v>1008.42692421531</v>
+        <v>870.7998288467744</v>
       </c>
       <c r="O36" t="n">
-        <v>1290.534329200916</v>
+        <v>1152.90723383238</v>
       </c>
       <c r="P36" t="n">
         <v>1300</v>
@@ -7046,13 +7046,13 @@
         <v>984.008637232401</v>
       </c>
       <c r="W36" t="n">
-        <v>655.7258089495728</v>
+        <v>969.490311060857</v>
       </c>
       <c r="X36" t="n">
-        <v>653.8442539542318</v>
+        <v>967.6087560655161</v>
       </c>
       <c r="Y36" t="n">
-        <v>653.8442539542318</v>
+        <v>682.5656565656566</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>399.5384397069486</v>
+        <v>411.4921839101395</v>
       </c>
       <c r="C37" t="n">
-        <v>399.5384397069486</v>
+        <v>555.3141897285752</v>
       </c>
       <c r="D37" t="n">
-        <v>399.5384397069486</v>
+        <v>686.4533338535753</v>
       </c>
       <c r="E37" t="n">
-        <v>399.5384397069486</v>
+        <v>822.1022380649883</v>
       </c>
       <c r="F37" t="n">
-        <v>541.7194122988841</v>
+        <v>964.2832106569238</v>
       </c>
       <c r="G37" t="n">
-        <v>713.0977240874087</v>
+        <v>964.2832106569238</v>
       </c>
       <c r="H37" t="n">
-        <v>713.0977240874087</v>
+        <v>1152.968954832715</v>
       </c>
       <c r="I37" t="n">
-        <v>956.6140161382457</v>
+        <v>1295.432341311225</v>
       </c>
       <c r="J37" t="n">
-        <v>1278.364016138246</v>
+        <v>1295.432341311225</v>
       </c>
       <c r="K37" t="n">
-        <v>1278.364016138246</v>
+        <v>1295.432341311225</v>
       </c>
       <c r="L37" t="n">
         <v>1295.432341311225</v>
@@ -7101,7 +7101,7 @@
         <v>1084.994224286414</v>
       </c>
       <c r="O37" t="n">
-        <v>882.1858220870445</v>
+        <v>882.1858220870446</v>
       </c>
       <c r="P37" t="n">
         <v>628.7418456501357</v>
@@ -7113,25 +7113,25 @@
         <v>26</v>
       </c>
       <c r="S37" t="n">
-        <v>40.9767304230777</v>
+        <v>26</v>
       </c>
       <c r="T37" t="n">
-        <v>40.9767304230777</v>
+        <v>26</v>
       </c>
       <c r="U37" t="n">
-        <v>40.9767304230777</v>
+        <v>26</v>
       </c>
       <c r="V37" t="n">
-        <v>40.9767304230777</v>
+        <v>242.641392885946</v>
       </c>
       <c r="W37" t="n">
-        <v>230.6876486827551</v>
+        <v>242.641392885946</v>
       </c>
       <c r="X37" t="n">
-        <v>399.5384397069486</v>
+        <v>411.4921839101395</v>
       </c>
       <c r="Y37" t="n">
-        <v>399.5384397069486</v>
+        <v>411.4921839101395</v>
       </c>
     </row>
     <row r="38">
@@ -7168,22 +7168,22 @@
         <v>26</v>
       </c>
       <c r="K38" t="n">
-        <v>69.031941959799</v>
+        <v>347.75</v>
       </c>
       <c r="L38" t="n">
-        <v>122.4168711055276</v>
+        <v>401.1349291457287</v>
       </c>
       <c r="M38" t="n">
-        <v>334.75</v>
+        <v>608.137455018164</v>
       </c>
       <c r="N38" t="n">
-        <v>656.5</v>
+        <v>929.887455018164</v>
       </c>
       <c r="O38" t="n">
+        <v>929.887455018164</v>
+      </c>
+      <c r="P38" t="n">
         <v>978.25</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1300</v>
       </c>
       <c r="Q38" t="n">
         <v>1300</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>179.6382119054211</v>
+        <v>682.5656565656566</v>
       </c>
       <c r="C39" t="n">
-        <v>179.6382119054211</v>
+        <v>682.5656565656566</v>
       </c>
       <c r="D39" t="n">
-        <v>179.6382119054211</v>
+        <v>682.5656565656566</v>
       </c>
       <c r="E39" t="n">
-        <v>179.6382119054211</v>
+        <v>354.2828282828283</v>
       </c>
       <c r="F39" t="n">
-        <v>179.6382119054211</v>
+        <v>26</v>
       </c>
       <c r="G39" t="n">
-        <v>179.6382119054211</v>
+        <v>26</v>
       </c>
       <c r="H39" t="n">
-        <v>179.6382119054211</v>
+        <v>26</v>
       </c>
       <c r="I39" t="n">
         <v>26</v>
@@ -7250,7 +7250,7 @@
         <v>385.477880609305</v>
       </c>
       <c r="L39" t="n">
-        <v>558.5016784397432</v>
+        <v>690.4439701826024</v>
       </c>
       <c r="M39" t="n">
         <v>690.4439701826024</v>
@@ -7265,31 +7265,31 @@
         <v>1300</v>
       </c>
       <c r="Q39" t="n">
-        <v>1300</v>
+        <v>1148.746311229361</v>
       </c>
       <c r="R39" t="n">
-        <v>1180.886577920791</v>
+        <v>1029.632889150152</v>
       </c>
       <c r="S39" t="n">
-        <v>852.6037496379626</v>
+        <v>984.008637232401</v>
       </c>
       <c r="T39" t="n">
-        <v>852.6037496379626</v>
+        <v>984.008637232401</v>
       </c>
       <c r="U39" t="n">
-        <v>852.6037496379626</v>
+        <v>984.008637232401</v>
       </c>
       <c r="V39" t="n">
-        <v>524.3209213551343</v>
+        <v>984.008637232401</v>
       </c>
       <c r="W39" t="n">
-        <v>509.8025951835903</v>
+        <v>969.490311060857</v>
       </c>
       <c r="X39" t="n">
-        <v>507.9210401882494</v>
+        <v>682.5656565656566</v>
       </c>
       <c r="Y39" t="n">
-        <v>179.6382119054211</v>
+        <v>682.5656565656566</v>
       </c>
     </row>
     <row r="40">
@@ -7299,34 +7299,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>889.0331753964418</v>
+        <v>720.3350579741671</v>
       </c>
       <c r="C40" t="n">
-        <v>889.0331753964418</v>
+        <v>720.3350579741671</v>
       </c>
       <c r="D40" t="n">
-        <v>889.0331753964418</v>
+        <v>720.3350579741671</v>
       </c>
       <c r="E40" t="n">
-        <v>889.0331753964418</v>
+        <v>720.3350579741671</v>
       </c>
       <c r="F40" t="n">
-        <v>889.0331753964418</v>
+        <v>862.5160305661025</v>
       </c>
       <c r="G40" t="n">
-        <v>889.0331753964418</v>
+        <v>862.5160305661025</v>
       </c>
       <c r="H40" t="n">
-        <v>889.0331753964418</v>
+        <v>1051.201774741894</v>
       </c>
       <c r="I40" t="n">
-        <v>1132.549467447279</v>
+        <v>1051.201774741894</v>
       </c>
       <c r="J40" t="n">
-        <v>1132.549467447279</v>
+        <v>1295.432341311225</v>
       </c>
       <c r="K40" t="n">
-        <v>1278.364016138246</v>
+        <v>1295.432341311225</v>
       </c>
       <c r="L40" t="n">
         <v>1295.432341311225</v>
@@ -7350,25 +7350,25 @@
         <v>26</v>
       </c>
       <c r="S40" t="n">
-        <v>83.71477230728786</v>
+        <v>26</v>
       </c>
       <c r="T40" t="n">
-        <v>290.2588203185518</v>
+        <v>232.5440480112639</v>
       </c>
       <c r="U40" t="n">
-        <v>554.6382900060187</v>
+        <v>232.5440480112639</v>
       </c>
       <c r="V40" t="n">
-        <v>630.2265370511175</v>
+        <v>232.5440480112639</v>
       </c>
       <c r="W40" t="n">
-        <v>630.2265370511175</v>
+        <v>422.2549662709413</v>
       </c>
       <c r="X40" t="n">
-        <v>630.2265370511175</v>
+        <v>591.1057572951348</v>
       </c>
       <c r="Y40" t="n">
-        <v>759.4558377301497</v>
+        <v>720.3350579741671</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>186.7351812292086</v>
+        <v>26</v>
       </c>
       <c r="C41" t="n">
-        <v>186.7351812292086</v>
+        <v>26</v>
       </c>
       <c r="D41" t="n">
-        <v>186.7351812292086</v>
+        <v>26</v>
       </c>
       <c r="E41" t="n">
-        <v>186.7351812292086</v>
+        <v>26</v>
       </c>
       <c r="F41" t="n">
-        <v>89.876970413035</v>
+        <v>26</v>
       </c>
       <c r="G41" t="n">
         <v>26</v>
@@ -7411,13 +7411,13 @@
         <v>444.1668711055277</v>
       </c>
       <c r="M41" t="n">
-        <v>444.1668711055277</v>
+        <v>765.9168711055277</v>
       </c>
       <c r="N41" t="n">
-        <v>444.1668711055277</v>
+        <v>929.887455018164</v>
       </c>
       <c r="O41" t="n">
-        <v>656.5</v>
+        <v>929.887455018164</v>
       </c>
       <c r="P41" t="n">
         <v>978.25</v>
@@ -7429,25 +7429,25 @@
         <v>1300</v>
       </c>
       <c r="S41" t="n">
-        <v>1300</v>
+        <v>1285.627047221926</v>
       </c>
       <c r="T41" t="n">
-        <v>1300</v>
+        <v>1006.657600168557</v>
       </c>
       <c r="U41" t="n">
-        <v>1300</v>
+        <v>678.3747718856985</v>
       </c>
       <c r="V41" t="n">
-        <v>975.9080563971476</v>
+        <v>354.2828282828461</v>
       </c>
       <c r="W41" t="n">
-        <v>647.6252281143018</v>
+        <v>26</v>
       </c>
       <c r="X41" t="n">
-        <v>361.4819619924152</v>
+        <v>26</v>
       </c>
       <c r="Y41" t="n">
-        <v>361.4819619924152</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
@@ -7481,28 +7481,28 @@
         <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>167.0572291375631</v>
+        <v>29.43013376902758</v>
       </c>
       <c r="K42" t="n">
-        <v>385.477880609305</v>
+        <v>247.8507852407695</v>
       </c>
       <c r="L42" t="n">
-        <v>696.1287738082788</v>
+        <v>558.5016784397432</v>
       </c>
       <c r="M42" t="n">
-        <v>828.071065551138</v>
+        <v>690.4439701826024</v>
       </c>
       <c r="N42" t="n">
-        <v>1008.42692421531</v>
+        <v>870.7998288467744</v>
       </c>
       <c r="O42" t="n">
-        <v>1290.534329200916</v>
+        <v>1152.90723383238</v>
       </c>
       <c r="P42" t="n">
         <v>1300</v>
       </c>
       <c r="Q42" t="n">
-        <v>1300.000000000028</v>
+        <v>1300</v>
       </c>
       <c r="R42" t="n">
         <v>1076.491563767798</v>
@@ -7566,22 +7566,22 @@
         <v>1296.191357565129</v>
       </c>
       <c r="L43" t="n">
-        <v>1203.505228775188</v>
+        <v>1296.191357565129</v>
       </c>
       <c r="M43" t="n">
-        <v>1203.505228775188</v>
+        <v>1296.191357565129</v>
       </c>
       <c r="N43" t="n">
-        <v>1203.505228775188</v>
+        <v>1296.191357565129</v>
       </c>
       <c r="O43" t="n">
-        <v>1062.062878984691</v>
+        <v>983.2819452647493</v>
       </c>
       <c r="P43" t="n">
-        <v>733.7800507018001</v>
+        <v>733.7800507017898</v>
       </c>
       <c r="Q43" t="n">
-        <v>405.4972224189097</v>
+        <v>405.4972224189055</v>
       </c>
       <c r="R43" t="n">
         <v>77.21439413601891</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>268.5174042371584</v>
+        <v>643.4343434343065</v>
       </c>
       <c r="C44" t="n">
-        <v>268.5174042371584</v>
+        <v>513.3917918075707</v>
       </c>
       <c r="D44" t="n">
-        <v>268.5174042371584</v>
+        <v>411.0290082319649</v>
       </c>
       <c r="E44" t="n">
-        <v>172.1908490787052</v>
+        <v>314.7024530735117</v>
       </c>
       <c r="F44" t="n">
-        <v>172.1908490787052</v>
+        <v>217.8442422573381</v>
       </c>
       <c r="G44" t="n">
-        <v>76.8214917612278</v>
+        <v>122.4748849398607</v>
       </c>
       <c r="H44" t="n">
         <v>26</v>
@@ -7645,19 +7645,19 @@
         <v>69.031941959799</v>
       </c>
       <c r="L44" t="n">
-        <v>122.4168711055276</v>
+        <v>286.387455018164</v>
       </c>
       <c r="M44" t="n">
-        <v>444.1668711055277</v>
+        <v>608.137455018164</v>
       </c>
       <c r="N44" t="n">
-        <v>765.9168711055277</v>
+        <v>929.887455018164</v>
       </c>
       <c r="O44" t="n">
-        <v>1087.666871105528</v>
+        <v>929.887455018164</v>
       </c>
       <c r="P44" t="n">
-        <v>1136.029416087364</v>
+        <v>978.25</v>
       </c>
       <c r="Q44" t="n">
         <v>1300</v>
@@ -7672,19 +7672,19 @@
         <v>1300</v>
       </c>
       <c r="U44" t="n">
-        <v>1300</v>
+        <v>971.7171717171454</v>
       </c>
       <c r="V44" t="n">
-        <v>975.9080563971476</v>
+        <v>971.7171717171454</v>
       </c>
       <c r="W44" t="n">
-        <v>647.6252281143109</v>
+        <v>643.4343434343065</v>
       </c>
       <c r="X44" t="n">
-        <v>647.6252281143109</v>
+        <v>643.4343434343065</v>
       </c>
       <c r="Y44" t="n">
-        <v>443.264185000365</v>
+        <v>643.4343434343065</v>
       </c>
     </row>
     <row r="45">
@@ -7718,22 +7718,22 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>167.0572291375631</v>
+        <v>29.43013376902758</v>
       </c>
       <c r="K45" t="n">
-        <v>385.477880609305</v>
+        <v>247.8507852407695</v>
       </c>
       <c r="L45" t="n">
-        <v>696.1287738082788</v>
+        <v>558.5016784397432</v>
       </c>
       <c r="M45" t="n">
-        <v>828.071065551138</v>
+        <v>690.4439701826024</v>
       </c>
       <c r="N45" t="n">
-        <v>1008.42692421531</v>
+        <v>870.7998288467744</v>
       </c>
       <c r="O45" t="n">
-        <v>1290.534329200916</v>
+        <v>1152.90723383238</v>
       </c>
       <c r="P45" t="n">
         <v>1300</v>
@@ -7742,19 +7742,19 @@
         <v>1300</v>
       </c>
       <c r="R45" t="n">
-        <v>1076.491563767798</v>
+        <v>1070.785567819781</v>
       </c>
       <c r="S45" t="n">
-        <v>920.7663017490366</v>
+        <v>915.0603058010195</v>
       </c>
       <c r="T45" t="n">
-        <v>824.1796035114107</v>
+        <v>818.4736075633936</v>
       </c>
       <c r="U45" t="n">
-        <v>732.0600767858552</v>
+        <v>726.3540808378381</v>
       </c>
       <c r="V45" t="n">
-        <v>625.4836452792692</v>
+        <v>619.7776493312521</v>
       </c>
       <c r="W45" t="n">
         <v>500.8643090067152</v>
@@ -7806,22 +7806,22 @@
         <v>1296.191357565129</v>
       </c>
       <c r="M46" t="n">
-        <v>1106.691882560069</v>
+        <v>1296.191357565129</v>
       </c>
       <c r="N46" t="n">
-        <v>1106.691882560069</v>
+        <v>1296.191357565129</v>
       </c>
       <c r="O46" t="n">
-        <v>1062.062878984675</v>
+        <v>983.2819452647495</v>
       </c>
       <c r="P46" t="n">
-        <v>733.7800507017898</v>
+        <v>654.9991169819212</v>
       </c>
       <c r="Q46" t="n">
-        <v>405.4972224189046</v>
+        <v>354.2828282828283</v>
       </c>
       <c r="R46" t="n">
-        <v>77.21439413601888</v>
+        <v>26</v>
       </c>
       <c r="S46" t="n">
         <v>26</v>
@@ -7964,16 +7964,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>350.0409208179547</v>
+        <v>282.2177600646936</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>300.533391959799</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>828.2610974915635</v>
+        <v>484.2610974915635</v>
       </c>
       <c r="N2" t="n">
         <v>760.2770485220965</v>
@@ -7982,10 +7982,10 @@
         <v>12.67382434796179</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>295.148944462792</v>
       </c>
       <c r="Q2" t="n">
-        <v>319.7811816048552</v>
+        <v>135.9220059355256</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,7 +8043,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>227.4647419277884</v>
+        <v>163.6797971110859</v>
       </c>
       <c r="K3" t="n">
         <v>295.8802408630135</v>
@@ -8061,7 +8061,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P3" t="n">
-        <v>155.3657670238469</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8210,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>668.1202731608934</v>
+        <v>828.2610974915635</v>
       </c>
       <c r="N5" t="n">
         <v>760.2770485220965</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>479.9220059355256</v>
+        <v>319.7811816048552</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8286,10 +8286,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L6" t="n">
-        <v>388.0893364597981</v>
+        <v>324.3043916430955</v>
       </c>
       <c r="M6" t="n">
-        <v>407.9098756134048</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N6" t="n">
         <v>485.4085271713503</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>363.0409208179547</v>
+        <v>6.04092081795465</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>196.3339231440955</v>
       </c>
       <c r="M8" t="n">
-        <v>680.5950206356404</v>
+        <v>841.2610974915641</v>
       </c>
       <c r="N8" t="n">
-        <v>773.2770485220965</v>
+        <v>773.2770485220969</v>
       </c>
       <c r="O8" t="n">
         <v>12.67382434796179</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>492.9220059355257</v>
+        <v>492.9220059355262</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8517,7 +8517,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>215.1545445858333</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
         <v>295.8802408630135</v>
@@ -8535,7 +8535,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
-        <v>219.1507118405495</v>
+        <v>206.8405144986142</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>366.040920817957</v>
+        <v>366.0409208179584</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>844.2610974915659</v>
+        <v>844.2610974915673</v>
       </c>
       <c r="N11" t="n">
-        <v>776.2770485220988</v>
+        <v>776.2770485221001</v>
       </c>
       <c r="O11" t="n">
         <v>12.67382434796179</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>335.1347169583835</v>
+        <v>335.1347169584283</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8766,10 +8766,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N12" t="n">
-        <v>485.4085271713503</v>
+        <v>484.977117708232</v>
       </c>
       <c r="O12" t="n">
-        <v>382.2503893377937</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P12" t="n">
         <v>219.1507118405495</v>
@@ -8915,16 +8915,16 @@
         <v>6.04092081795465</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>316.5333919598113</v>
       </c>
       <c r="L14" t="n">
-        <v>199.2127110228593</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>844.2610974915655</v>
+        <v>844.2610974915668</v>
       </c>
       <c r="N14" t="n">
-        <v>776.2770485220983</v>
+        <v>776.2770485220997</v>
       </c>
       <c r="O14" t="n">
         <v>12.67382434796179</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>495.9220059355275</v>
+        <v>378.6013249986215</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9006,7 +9006,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>382.2503893377365</v>
+        <v>382.2503893377855</v>
       </c>
       <c r="P15" t="n">
         <v>219.1507118405495</v>
@@ -9155,13 +9155,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>199.2127110228607</v>
+        <v>199.2127110229036</v>
       </c>
       <c r="M17" t="n">
-        <v>844.261097491565</v>
+        <v>844.2610974915659</v>
       </c>
       <c r="N17" t="n">
-        <v>776.2770485220979</v>
+        <v>776.2770485220988</v>
       </c>
       <c r="O17" t="n">
         <v>12.67382434796179</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>495.9220059355271</v>
+        <v>495.922005935528</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9240,10 +9240,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N18" t="n">
-        <v>484.977117708183</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>382.6817988009037</v>
+        <v>382.2503893377822</v>
       </c>
       <c r="P18" t="n">
         <v>219.1507118405495</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>366.0409208179562</v>
+        <v>366.0409208179571</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>316.5333919598114</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>844.261097491565</v>
+        <v>844.2610974915659</v>
       </c>
       <c r="N20" t="n">
-        <v>776.2770485220981</v>
+        <v>658.9563675851919</v>
       </c>
       <c r="O20" t="n">
         <v>12.67382434796179</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>335.134716958386</v>
+        <v>135.9220059355256</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9480,7 +9480,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O21" t="n">
-        <v>382.2503893377365</v>
+        <v>382.2503893377855</v>
       </c>
       <c r="P21" t="n">
         <v>219.1507118405495</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>6.04092081795465</v>
+        <v>366.0409208179577</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>316.5333919598113</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>732.324864051631</v>
+        <v>484.2610974915635</v>
       </c>
       <c r="N23" t="n">
-        <v>416.2770485220965</v>
+        <v>658.9563675851887</v>
       </c>
       <c r="O23" t="n">
-        <v>372.6738243479636</v>
+        <v>12.67382434796179</v>
       </c>
       <c r="P23" t="n">
-        <v>311.1489444627938</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>495.9220059355274</v>
+        <v>495.9220059355287</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9717,7 +9717,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>382.2503893377898</v>
+        <v>382.2503893377811</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>347.0409208179547</v>
+        <v>6.04092081795465</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>180.9803877905537</v>
       </c>
       <c r="M26" t="n">
-        <v>665.2414852821055</v>
+        <v>825.2610974915759</v>
       </c>
       <c r="N26" t="n">
-        <v>757.2770485220965</v>
+        <v>757.2770485221088</v>
       </c>
       <c r="O26" t="n">
         <v>12.67382434796179</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>476.9220059355256</v>
+        <v>476.922005935538</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9948,7 +9948,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M27" t="n">
-        <v>396.0310877346169</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N27" t="n">
         <v>485.4085271713503</v>
@@ -9957,7 +9957,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P27" t="n">
-        <v>219.1507118405495</v>
+        <v>143.4869791451077</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>347.0409208179547</v>
+        <v>6.04092081795465</v>
       </c>
       <c r="K29" t="n">
-        <v>297.533391959799</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>180.9803877905537</v>
       </c>
       <c r="M29" t="n">
-        <v>708.7080933223065</v>
+        <v>825.2610974915759</v>
       </c>
       <c r="N29" t="n">
-        <v>757.2770485220965</v>
+        <v>757.2770485221088</v>
       </c>
       <c r="O29" t="n">
         <v>12.67382434796179</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>135.9220059355256</v>
+        <v>476.922005935538</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10194,7 +10194,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P30" t="n">
-        <v>143.4869791450588</v>
+        <v>143.4869791451077</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10340,22 +10340,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>168.5056403157943</v>
       </c>
       <c r="M32" t="n">
-        <v>812.261097491565</v>
+        <v>812.2610974915635</v>
       </c>
       <c r="N32" t="n">
-        <v>744.2770485220979</v>
+        <v>744.2770485220965</v>
       </c>
       <c r="O32" t="n">
-        <v>340.6738243479633</v>
+        <v>12.67382434796179</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>304.4276462513157</v>
+        <v>463.9220059355256</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10419,7 +10419,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L33" t="n">
-        <v>260.9508562895601</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M33" t="n">
         <v>471.6948204301074</v>
@@ -10428,7 +10428,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O33" t="n">
-        <v>382.6817988009037</v>
+        <v>255.5433186306658</v>
       </c>
       <c r="P33" t="n">
         <v>219.1507118405495</v>
@@ -10574,10 +10574,10 @@
         <v>6.04092081795465</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>281.533391959799</v>
       </c>
       <c r="L35" t="n">
-        <v>271.0758291457287</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>809.2610974915635</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>355.4730292268034</v>
+        <v>345.0154664127331</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10662,13 +10662,13 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>346.3912591223244</v>
       </c>
       <c r="O36" t="n">
         <v>382.6817988009037</v>
       </c>
       <c r="P36" t="n">
-        <v>80.13344379152367</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10811,25 +10811,25 @@
         <v>6.04092081795465</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>281.533391959799</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>698.7390054657781</v>
+        <v>693.3545579687709</v>
       </c>
       <c r="N38" t="n">
         <v>741.2770485220965</v>
       </c>
       <c r="O38" t="n">
-        <v>337.6738243479618</v>
+        <v>12.67382434796179</v>
       </c>
       <c r="P38" t="n">
-        <v>276.148944462792</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>135.9220059355256</v>
+        <v>460.9220059355256</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10893,10 +10893,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>249.0720684107723</v>
+        <v>382.3471105752765</v>
       </c>
       <c r="M39" t="n">
-        <v>471.6948204301074</v>
+        <v>338.4197782656032</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
@@ -11054,16 +11054,16 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>484.2610974915635</v>
+        <v>809.2610974915635</v>
       </c>
       <c r="N41" t="n">
-        <v>416.2770485220965</v>
+        <v>581.903900959103</v>
       </c>
       <c r="O41" t="n">
-        <v>227.1517323221762</v>
+        <v>12.67382434796179</v>
       </c>
       <c r="P41" t="n">
-        <v>276.148944462792</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>460.9220059355256</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>88.44747387876262</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11142,7 +11142,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P42" t="n">
-        <v>80.13344379152367</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11288,7 +11288,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>165.6268524370064</v>
       </c>
       <c r="M44" t="n">
         <v>809.2610974915635</v>
@@ -11297,13 +11297,13 @@
         <v>741.2770485220965</v>
       </c>
       <c r="O44" t="n">
-        <v>337.6738243479618</v>
+        <v>12.67382434796179</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>301.548858372532</v>
+        <v>460.9220059355256</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,7 +11361,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>88.44747387876262</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
@@ -11379,7 +11379,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
-        <v>80.13344379152367</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22515,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>44.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>5.602231819936407</v>
+        <v>50.07681006293035</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -23280,13 +23280,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>125.1627282125276</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>125.1627282125753</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.409285400154005</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23426,7 +23426,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.409285400105944</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23460,13 +23460,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>18.17027608003843</v>
       </c>
       <c r="C14" t="n">
         <v>54.47457824299391</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>15.33915573984979</v>
       </c>
       <c r="E14" t="n">
         <v>9.363289606868648</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>33.50943181993622</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.409285400153976</v>
+        <v>3.409285400106228</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -24408,22 +24408,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>167.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>135.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>96.33915573984979</v>
       </c>
       <c r="E26" t="n">
-        <v>90.36328960686865</v>
+        <v>30.25651839305426</v>
       </c>
       <c r="F26" t="n">
         <v>90.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>89.41566374430265</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24459,25 +24459,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>173.0614843852375</v>
       </c>
       <c r="T26" t="n">
         <v>271.1797525828352</v>
       </c>
       <c r="U26" t="n">
-        <v>231.8222222222355</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>315.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>278.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>197.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>86.75926750204147</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24605,19 +24605,19 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>304.7803181773756</v>
       </c>
       <c r="P28" t="n">
-        <v>13.90953667253977</v>
+        <v>262.3519902237796</v>
       </c>
       <c r="Q28" t="n">
-        <v>399.004266425598</v>
+        <v>58.00426642558566</v>
       </c>
       <c r="R28" t="n">
-        <v>144.4714147999746</v>
+        <v>64.71016076802397</v>
       </c>
       <c r="S28" t="n">
-        <v>45.70225019465872</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>89.41566374430265</v>
       </c>
       <c r="H29" t="n">
-        <v>90.51013609046208</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,10 +24696,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>173.0614843852375</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>13.75554868621435</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -24708,7 +24708,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>96.3068969810378</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>278.2818334606677</v>
@@ -24833,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>86.75926750204147</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>182.6044802550089</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24845,16 +24845,16 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>354.9095366725398</v>
+        <v>13.90953667252743</v>
       </c>
       <c r="Q31" t="n">
-        <v>270.2270381542367</v>
+        <v>58.00426642558566</v>
       </c>
       <c r="R31" t="n">
-        <v>64.7101607680363</v>
+        <v>302.8669345449425</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>45.70225019465872</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25122,7 +25122,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1.472854323080476</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.472854323080426</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>172.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>140.4745782429939</v>
@@ -25605,10 +25605,10 @@
         <v>95.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>95.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>31.177463035398</v>
+        <v>94.41566374430265</v>
       </c>
       <c r="H41" t="n">
         <v>95.51013609046208</v>
@@ -25644,22 +25644,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>178.0614843852375</v>
+        <v>163.8322611349444</v>
       </c>
       <c r="T41" t="n">
-        <v>276.1797525828352</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>340.1939598651936</v>
+        <v>15.19395986516361</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>4.373475980930152</v>
+        <v>4.373475980929925</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>283.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>202.3174326828064</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>5.648935988509578</v>
+        <v>5.648935988536806</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>91.75926750204147</v>
       </c>
       <c r="M43" t="n">
         <v>187.6044802550089</v>
@@ -25790,16 +25790,16 @@
         <v>238.7292555995538</v>
       </c>
       <c r="O43" t="n">
-        <v>169.7523918847842</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>34.90953667247732</v>
+        <v>112.9026610552099</v>
       </c>
       <c r="Q43" t="n">
-        <v>79.00426642553657</v>
+        <v>79.00426642554248</v>
       </c>
       <c r="R43" t="n">
-        <v>85.71016076797446</v>
+        <v>85.71016076797855</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>172.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>140.4745782429939</v>
+        <v>11.73245213252551</v>
       </c>
       <c r="D44" t="n">
-        <v>101.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>95.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>45.19685924684656</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25887,19 +25887,19 @@
         <v>276.1797525828352</v>
       </c>
       <c r="U44" t="n">
-        <v>340.1939598651936</v>
+        <v>15.1939598651677</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>320.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>4.373475980939247</v>
+        <v>4.373475980936973</v>
       </c>
       <c r="X44" t="n">
         <v>283.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>202.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>5.648935988536778</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>5.648935988537005</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26021,25 +26021,25 @@
         <v>91.75926750204144</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>187.6044802550089</v>
       </c>
       <c r="N46" t="n">
         <v>238.7292555995538</v>
       </c>
       <c r="O46" t="n">
-        <v>265.5976046377352</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>34.90953667248323</v>
+        <v>34.90953667253979</v>
       </c>
       <c r="Q46" t="n">
-        <v>79.00426642554157</v>
+        <v>106.295140613496</v>
       </c>
       <c r="R46" t="n">
-        <v>85.71016076797946</v>
+        <v>85.7101607680363</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>50.70225019465869</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>897731.2378626261</v>
+        <v>897731.237862626</v>
       </c>
     </row>
     <row r="3">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2409417.981449497</v>
+        <v>2409417.981449499</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3159669.485494407</v>
+        <v>3159669.485494411</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3909268.844084768</v>
+        <v>3909268.844084777</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4664895.068284324</v>
+        <v>4664895.068284333</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5420521.292483878</v>
+        <v>5420521.292483887</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6176147.516683433</v>
+        <v>6176147.516683441</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6854050.488293532</v>
+        <v>6854050.488293544</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7536083.714449087</v>
+        <v>7536083.714449101</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8288883.97501228</v>
+        <v>8288883.97501229</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9043787.710234826</v>
+        <v>9043787.710234838</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9799343.590911917</v>
+        <v>9799343.590911929</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10473399.92368139</v>
+        <v>10473399.9236814</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11147456.25645085</v>
+        <v>11147456.25645086</v>
       </c>
     </row>
   </sheetData>
@@ -26278,25 +26278,25 @@
         <v>1448283.596382484</v>
       </c>
       <c r="E2" t="n">
-        <v>1436732.103964861</v>
+        <v>1436732.103964866</v>
       </c>
       <c r="F2" t="n">
-        <v>1436732.103964861</v>
+        <v>1436732.103964867</v>
       </c>
       <c r="G2" t="n">
-        <v>1448283.596382485</v>
+        <v>1448283.596382484</v>
       </c>
       <c r="H2" t="n">
         <v>1448283.596382484</v>
       </c>
       <c r="I2" t="n">
-        <v>1448283.596382484</v>
+        <v>1448283.596382485</v>
       </c>
       <c r="J2" t="n">
-        <v>1307230.350131488</v>
+        <v>1307230.350131494</v>
       </c>
       <c r="K2" t="n">
-        <v>1307230.350131488</v>
+        <v>1307230.350131494</v>
       </c>
       <c r="L2" t="n">
         <v>1448283.596382484</v>
@@ -26308,7 +26308,7 @@
         <v>1448148.771297749</v>
       </c>
       <c r="O2" t="n">
-        <v>1291941.304474797</v>
+        <v>1291941.304474796</v>
       </c>
       <c r="P2" t="n">
         <v>1291941.304474797</v>
@@ -26327,7 +26327,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4576</v>
+        <v>4576.000000004342</v>
       </c>
       <c r="E3" t="n">
         <v>313056</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>656082.1472563096</v>
+        <v>656067.3529384265</v>
       </c>
       <c r="C4" t="n">
-        <v>654045.5441927382</v>
+        <v>654030.749874855</v>
       </c>
       <c r="D4" t="n">
-        <v>653677.2190129204</v>
+        <v>653662.1353582595</v>
       </c>
       <c r="E4" t="n">
-        <v>645840.0212504843</v>
+        <v>645824.8708258005</v>
       </c>
       <c r="F4" t="n">
-        <v>643826.4582339064</v>
+        <v>643811.3078092225</v>
       </c>
       <c r="G4" t="n">
-        <v>647431.8849283078</v>
+        <v>647416.734503621</v>
       </c>
       <c r="H4" t="n">
-        <v>645389.5681216023</v>
+        <v>645374.4176969155</v>
       </c>
       <c r="I4" t="n">
-        <v>643344.4002074858</v>
+        <v>643329.2497827993</v>
       </c>
       <c r="J4" t="n">
-        <v>574027.5652474628</v>
+        <v>574012.8376996075</v>
       </c>
       <c r="K4" t="n">
-        <v>572240.729855191</v>
+        <v>572226.0023073358</v>
       </c>
       <c r="L4" t="n">
-        <v>638350.3309548979</v>
+        <v>638335.8927438178</v>
       </c>
       <c r="M4" t="n">
-        <v>636299.8796754016</v>
+        <v>636285.508234347</v>
       </c>
       <c r="N4" t="n">
-        <v>634201.8428761105</v>
+        <v>634187.4714350561</v>
       </c>
       <c r="O4" t="n">
-        <v>558369.627636163</v>
+        <v>558355.2561951079</v>
       </c>
       <c r="P4" t="n">
-        <v>556583.3681435883</v>
+        <v>556568.9967025338</v>
       </c>
     </row>
     <row r="5">
@@ -26431,28 +26431,28 @@
         <v>56816.145</v>
       </c>
       <c r="D5" t="n">
-        <v>57606.545</v>
+        <v>57606.54500000075</v>
       </c>
       <c r="E5" t="n">
-        <v>56948.255</v>
+        <v>56948.25500000075</v>
       </c>
       <c r="F5" t="n">
-        <v>56948.255</v>
+        <v>56948.25500000075</v>
       </c>
       <c r="G5" t="n">
-        <v>57704.876</v>
+        <v>57704.87600000075</v>
       </c>
       <c r="H5" t="n">
-        <v>57704.876</v>
+        <v>57704.87600000075</v>
       </c>
       <c r="I5" t="n">
-        <v>57704.876</v>
+        <v>57704.87600000075</v>
       </c>
       <c r="J5" t="n">
-        <v>48983.466</v>
+        <v>48983.46600000075</v>
       </c>
       <c r="K5" t="n">
-        <v>48983.466</v>
+        <v>48983.46600000075</v>
       </c>
       <c r="L5" t="n">
         <v>56852.173</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>522838.2729330137</v>
+        <v>522853.0672508966</v>
       </c>
       <c r="C6" t="n">
-        <v>732837.8759965844</v>
+        <v>732852.6703144681</v>
       </c>
       <c r="D6" t="n">
-        <v>732423.8323695634</v>
+        <v>732438.9160242194</v>
       </c>
       <c r="E6" t="n">
-        <v>420887.8277143765</v>
+        <v>420902.9781390651</v>
       </c>
       <c r="F6" t="n">
-        <v>735957.3907309541</v>
+        <v>735972.5411556434</v>
       </c>
       <c r="G6" t="n">
-        <v>731946.8354541766</v>
+        <v>731961.9858788626</v>
       </c>
       <c r="H6" t="n">
-        <v>745189.152260882</v>
+        <v>745204.3026855679</v>
       </c>
       <c r="I6" t="n">
-        <v>747234.3201749985</v>
+        <v>747249.4705996845</v>
       </c>
       <c r="J6" t="n">
-        <v>329819.3188840253</v>
+        <v>329834.0464318857</v>
       </c>
       <c r="K6" t="n">
-        <v>686006.1542762972</v>
+        <v>686020.8818241574</v>
       </c>
       <c r="L6" t="n">
-        <v>659481.0924275864</v>
+        <v>659495.5306386666</v>
       </c>
       <c r="M6" t="n">
-        <v>754295.0496223483</v>
+        <v>754309.4210634027</v>
       </c>
       <c r="N6" t="n">
-        <v>757193.0864216387</v>
+        <v>757207.4578626934</v>
       </c>
       <c r="O6" t="n">
-        <v>533181.3558386341</v>
+        <v>533195.7272796885</v>
       </c>
       <c r="P6" t="n">
-        <v>687767.6153312083</v>
+        <v>687781.9867722628</v>
       </c>
     </row>
   </sheetData>
@@ -26865,28 +26865,28 @@
         <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>357</v>
+        <v>357.0000000000123</v>
       </c>
       <c r="E4" t="n">
-        <v>360</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="F4" t="n">
-        <v>360</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="G4" t="n">
-        <v>360</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="H4" t="n">
-        <v>360</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="I4" t="n">
-        <v>360</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="J4" t="n">
-        <v>341</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="K4" t="n">
-        <v>341</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="L4" t="n">
         <v>328</v>
@@ -26975,10 +26975,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>390</v>
@@ -27008,7 +27008,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>191</v>
@@ -27082,7 +27082,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>13.00000000000523</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -27323,7 +27323,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>13.00000000001234</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
@@ -27442,7 +27442,7 @@
         <v>405</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068687</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
         <v>404.8896287080118</v>
@@ -27563,25 +27563,25 @@
         <v>405</v>
       </c>
       <c r="S3" t="n">
-        <v>405</v>
+        <v>119.1680093985736</v>
       </c>
       <c r="T3" t="n">
-        <v>404.6208312552496</v>
+        <v>90.03562054333543</v>
       </c>
       <c r="U3" t="n">
-        <v>400.1983314582999</v>
+        <v>56.19833145829995</v>
       </c>
       <c r="V3" t="n">
         <v>405</v>
       </c>
       <c r="W3" t="n">
-        <v>133.7200592412717</v>
+        <v>405</v>
       </c>
       <c r="X3" t="n">
-        <v>75.86273944538755</v>
+        <v>405</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27609,10 +27609,10 @@
         <v>405</v>
       </c>
       <c r="H4" t="n">
-        <v>297.3777837614428</v>
+        <v>405</v>
       </c>
       <c r="I4" t="n">
-        <v>172.0239474233969</v>
+        <v>405</v>
       </c>
       <c r="J4" t="n">
         <v>24.43214555721923</v>
@@ -27621,7 +27621,7 @@
         <v>270.7125770798316</v>
       </c>
       <c r="L4" t="n">
-        <v>400.7592675020414</v>
+        <v>405</v>
       </c>
       <c r="M4" t="n">
         <v>405</v>
@@ -27645,19 +27645,19 @@
         <v>405</v>
       </c>
       <c r="T4" t="n">
-        <v>405</v>
+        <v>209.3696484734708</v>
       </c>
       <c r="U4" t="n">
         <v>150.9500306187202</v>
       </c>
       <c r="V4" t="n">
+        <v>276.8621858048082</v>
+      </c>
+      <c r="W4" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X4" t="n">
         <v>405</v>
-      </c>
-      <c r="W4" t="n">
-        <v>405</v>
-      </c>
-      <c r="X4" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27679,7 +27679,7 @@
         <v>405</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068686</v>
+        <v>404.3632896068687</v>
       </c>
       <c r="F5" t="n">
         <v>404.8896287080118</v>
@@ -27758,7 +27758,7 @@
         <v>3.937686897702633</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>330.40233246944</v>
       </c>
       <c r="I6" t="n">
-        <v>210.8315745705938</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>191.922287858417</v>
+        <v>349.9037060657328</v>
       </c>
       <c r="S6" t="n">
-        <v>360.3326080501549</v>
+        <v>405</v>
       </c>
       <c r="T6" t="n">
         <v>404.6208312552496</v>
@@ -27809,7 +27809,7 @@
         <v>400.1983314582999</v>
       </c>
       <c r="V6" t="n">
-        <v>405</v>
+        <v>70.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>405</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>345.3516251750945</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>345.7867124617844</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>405</v>
       </c>
       <c r="E7" t="n">
         <v>405</v>
@@ -27855,7 +27855,7 @@
         <v>368.4321455572193</v>
       </c>
       <c r="K7" t="n">
-        <v>405</v>
+        <v>270.7125770798316</v>
       </c>
       <c r="L7" t="n">
         <v>400.7592675020414</v>
@@ -27916,13 +27916,13 @@
         <v>405</v>
       </c>
       <c r="E8" t="n">
-        <v>403.9896996697988</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
         <v>404.8896287080118</v>
       </c>
       <c r="G8" t="n">
-        <v>403.4156637443027</v>
+        <v>403.0420738072135</v>
       </c>
       <c r="H8" t="n">
         <v>404.5101360904621</v>
@@ -27992,13 +27992,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.5567056863481</v>
@@ -28007,7 +28007,7 @@
         <v>330.40233246944</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>210.8315745705938</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,19 +28034,19 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>308.5379024928325</v>
+        <v>405</v>
       </c>
       <c r="S9" t="n">
         <v>405</v>
       </c>
       <c r="T9" t="n">
-        <v>404.6208312552496</v>
+        <v>114.2425627503702</v>
       </c>
       <c r="U9" t="n">
         <v>400.1983314582999</v>
       </c>
       <c r="V9" t="n">
-        <v>405</v>
+        <v>57.51066719151967</v>
       </c>
       <c r="W9" t="n">
         <v>405</v>
@@ -28055,7 +28055,7 @@
         <v>405</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>42.39139276613386</v>
       </c>
     </row>
     <row r="10">
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>405</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>405</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>287.9856686280759</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28089,13 +28089,13 @@
         <v>172.0239474233969</v>
       </c>
       <c r="J10" t="n">
-        <v>381.4321455572193</v>
+        <v>24.43214555721923</v>
       </c>
       <c r="K10" t="n">
-        <v>405</v>
+        <v>270.7125770798316</v>
       </c>
       <c r="L10" t="n">
-        <v>405</v>
+        <v>400.7592675020414</v>
       </c>
       <c r="M10" t="n">
         <v>405</v>
@@ -28116,13 +28116,13 @@
         <v>405</v>
       </c>
       <c r="S10" t="n">
+        <v>359.7022501946587</v>
+      </c>
+      <c r="T10" t="n">
         <v>405</v>
       </c>
-      <c r="T10" t="n">
-        <v>370.8344677452089</v>
-      </c>
       <c r="U10" t="n">
-        <v>150.9500306187202</v>
+        <v>405</v>
       </c>
       <c r="V10" t="n">
         <v>405</v>
@@ -28223,19 +28223,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.55655664632425</v>
+        <v>24.55655664632289</v>
       </c>
       <c r="C12" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>325.5567056863481</v>
@@ -28244,7 +28244,7 @@
         <v>330.40233246944</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>210.8315745705938</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28280,19 +28280,19 @@
         <v>395</v>
       </c>
       <c r="U12" t="n">
-        <v>395</v>
+        <v>355.5333315189459</v>
       </c>
       <c r="V12" t="n">
         <v>395</v>
       </c>
       <c r="W12" t="n">
-        <v>234.3995840878188</v>
+        <v>395</v>
       </c>
       <c r="X12" t="n">
         <v>395</v>
       </c>
       <c r="Y12" t="n">
-        <v>39.39139276613204</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13">
@@ -28302,10 +28302,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>303.525956899876</v>
+        <v>395</v>
       </c>
       <c r="C13" t="n">
-        <v>272.7252466480447</v>
+        <v>395</v>
       </c>
       <c r="D13" t="n">
         <v>395</v>
@@ -28317,7 +28317,7 @@
         <v>395</v>
       </c>
       <c r="G13" t="n">
-        <v>244.8905941530055</v>
+        <v>395</v>
       </c>
       <c r="H13" t="n">
         <v>395</v>
@@ -28326,10 +28326,10 @@
         <v>395</v>
       </c>
       <c r="J13" t="n">
-        <v>24.43214555721923</v>
+        <v>27.80707035456273</v>
       </c>
       <c r="K13" t="n">
-        <v>395</v>
+        <v>395.0000000000014</v>
       </c>
       <c r="L13" t="n">
         <v>395</v>
@@ -28353,22 +28353,22 @@
         <v>395</v>
       </c>
       <c r="S13" t="n">
-        <v>359.7022501946587</v>
+        <v>395</v>
       </c>
       <c r="T13" t="n">
-        <v>395</v>
+        <v>209.3696484734708</v>
       </c>
       <c r="U13" t="n">
         <v>150.9500306187202</v>
       </c>
       <c r="V13" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W13" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X13" t="n">
         <v>395</v>
-      </c>
-      <c r="W13" t="n">
-        <v>395</v>
-      </c>
-      <c r="X13" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y13" t="n">
         <v>287.4653528494624</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>329.4510128528678</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
@@ -28469,13 +28469,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.5567056863481</v>
       </c>
       <c r="H15" t="n">
         <v>330.40233246944</v>
@@ -28505,10 +28505,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>149.7411518829324</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>315.8244475295484</v>
+        <v>175.922287858412</v>
       </c>
       <c r="S15" t="n">
         <v>395</v>
@@ -28520,10 +28520,10 @@
         <v>395</v>
       </c>
       <c r="V15" t="n">
-        <v>395</v>
+        <v>54.51066719151694</v>
       </c>
       <c r="W15" t="n">
-        <v>395</v>
+        <v>72.3731429098253</v>
       </c>
       <c r="X15" t="n">
         <v>395</v>
@@ -28542,13 +28542,13 @@
         <v>395</v>
       </c>
       <c r="C16" t="n">
-        <v>395</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D16" t="n">
-        <v>395</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
-        <v>395</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F16" t="n">
         <v>274.3828559677419</v>
@@ -28557,10 +28557,10 @@
         <v>395</v>
       </c>
       <c r="H16" t="n">
+        <v>227.4083392163727</v>
+      </c>
+      <c r="I16" t="n">
         <v>395</v>
-      </c>
-      <c r="I16" t="n">
-        <v>242.8302315177261</v>
       </c>
       <c r="J16" t="n">
         <v>24.43214555721923</v>
@@ -28596,10 +28596,10 @@
         <v>209.3696484734708</v>
       </c>
       <c r="U16" t="n">
-        <v>150.9500306187202</v>
+        <v>395</v>
       </c>
       <c r="V16" t="n">
-        <v>199.1703102162162</v>
+        <v>316.2998635957819</v>
       </c>
       <c r="W16" t="n">
         <v>395</v>
@@ -28624,7 +28624,7 @@
         <v>404</v>
       </c>
       <c r="D17" t="n">
-        <v>403.7470644682728</v>
+        <v>404</v>
       </c>
       <c r="E17" t="n">
         <v>404</v>
@@ -28639,7 +28639,7 @@
         <v>404</v>
       </c>
       <c r="I17" t="n">
-        <v>136.9074410897198</v>
+        <v>136.6545055579479</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,22 +28700,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>1.099912445516978</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>325.5567056863481</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>330.40233246944</v>
       </c>
       <c r="I18" t="n">
         <v>210.8315745705938</v>
@@ -28757,16 +28757,16 @@
         <v>400.1983314582999</v>
       </c>
       <c r="V18" t="n">
-        <v>240.9555733049374</v>
+        <v>404</v>
       </c>
       <c r="W18" t="n">
-        <v>72.37314290982712</v>
+        <v>404</v>
       </c>
       <c r="X18" t="n">
         <v>404</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>296.3350000606479</v>
       </c>
     </row>
     <row r="19">
@@ -28785,10 +28785,10 @@
         <v>404</v>
       </c>
       <c r="E19" t="n">
-        <v>280.9809048369565</v>
+        <v>404</v>
       </c>
       <c r="F19" t="n">
-        <v>404</v>
+        <v>278.2645056515061</v>
       </c>
       <c r="G19" t="n">
         <v>244.8905941530055</v>
@@ -28797,13 +28797,13 @@
         <v>227.4083392163727</v>
       </c>
       <c r="I19" t="n">
-        <v>404</v>
+        <v>172.0239474233969</v>
       </c>
       <c r="J19" t="n">
-        <v>353.2600313719311</v>
+        <v>24.43214555721923</v>
       </c>
       <c r="K19" t="n">
-        <v>404</v>
+        <v>270.7125770798316</v>
       </c>
       <c r="L19" t="n">
         <v>400.7592675020414</v>
@@ -28827,16 +28827,16 @@
         <v>404</v>
       </c>
       <c r="S19" t="n">
-        <v>359.7022501946587</v>
+        <v>404</v>
       </c>
       <c r="T19" t="n">
-        <v>209.3696484734708</v>
+        <v>404</v>
       </c>
       <c r="U19" t="n">
-        <v>150.9500306187202</v>
+        <v>404</v>
       </c>
       <c r="V19" t="n">
-        <v>199.1703102162162</v>
+        <v>404</v>
       </c>
       <c r="W19" t="n">
         <v>404</v>
@@ -28864,7 +28864,7 @@
         <v>404</v>
       </c>
       <c r="E20" t="n">
-        <v>404</v>
+        <v>403.7470644682272</v>
       </c>
       <c r="F20" t="n">
         <v>404</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>229.1608140503362</v>
+        <v>229.4137495820632</v>
       </c>
       <c r="S20" t="n">
         <v>404</v>
@@ -28934,13 +28934,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>91.60507348593973</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>1.099912445517774</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -28994,13 +28994,13 @@
         <v>400.1983314582999</v>
       </c>
       <c r="V21" t="n">
-        <v>404</v>
+        <v>54.51066719151774</v>
       </c>
       <c r="W21" t="n">
-        <v>404</v>
+        <v>96.7374233049581</v>
       </c>
       <c r="X21" t="n">
-        <v>404</v>
+        <v>59.86273944538513</v>
       </c>
       <c r="Y21" t="n">
         <v>399.3913927661343</v>
@@ -29013,19 +29013,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>287.1138003370787</v>
+        <v>404</v>
       </c>
       <c r="C22" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D22" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E22" t="n">
         <v>404</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>404</v>
-      </c>
-      <c r="E22" t="n">
-        <v>280.9809048369565</v>
-      </c>
-      <c r="F22" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G22" t="n">
         <v>404</v>
@@ -29034,16 +29034,16 @@
         <v>404</v>
       </c>
       <c r="I22" t="n">
-        <v>404</v>
+        <v>172.0239474233969</v>
       </c>
       <c r="J22" t="n">
         <v>24.43214555721923</v>
       </c>
       <c r="K22" t="n">
-        <v>404</v>
+        <v>270.7125770798316</v>
       </c>
       <c r="L22" t="n">
-        <v>404</v>
+        <v>400.7592675020414</v>
       </c>
       <c r="M22" t="n">
         <v>404</v>
@@ -29064,19 +29064,19 @@
         <v>404</v>
       </c>
       <c r="S22" t="n">
-        <v>404</v>
+        <v>359.7022501946587</v>
       </c>
       <c r="T22" t="n">
-        <v>305.9975174903007</v>
+        <v>216.558691783475</v>
       </c>
       <c r="U22" t="n">
         <v>150.9500306187202</v>
       </c>
       <c r="V22" t="n">
-        <v>199.1703102162162</v>
+        <v>404</v>
       </c>
       <c r="W22" t="n">
-        <v>226.3728098387097</v>
+        <v>404</v>
       </c>
       <c r="X22" t="n">
         <v>404</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>229.1608140503362</v>
+        <v>229.1608140502925</v>
       </c>
       <c r="S23" t="n">
         <v>404</v>
@@ -29174,13 +29174,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>50.8205265069912</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>149.7411518829367</v>
       </c>
       <c r="R24" t="n">
         <v>404</v>
@@ -29228,16 +29228,16 @@
         <v>404</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1983314582999</v>
+        <v>274.8214599705015</v>
       </c>
       <c r="V24" t="n">
-        <v>404</v>
+        <v>54.51066719151711</v>
       </c>
       <c r="W24" t="n">
-        <v>404</v>
+        <v>72.37314290982548</v>
       </c>
       <c r="X24" t="n">
-        <v>404</v>
+        <v>59.86273944538451</v>
       </c>
       <c r="Y24" t="n">
         <v>399.3913927661343</v>
@@ -29250,37 +29250,37 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>404</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C25" t="n">
-        <v>404</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D25" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E25" t="n">
-        <v>280.9809048369565</v>
+        <v>404</v>
       </c>
       <c r="F25" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G25" t="n">
-        <v>244.8905941530055</v>
+        <v>404</v>
       </c>
       <c r="H25" t="n">
         <v>404</v>
       </c>
       <c r="I25" t="n">
-        <v>220.7557810918716</v>
+        <v>404</v>
       </c>
       <c r="J25" t="n">
-        <v>24.43214555721923</v>
+        <v>364.3141018579433</v>
       </c>
       <c r="K25" t="n">
-        <v>270.7125770798316</v>
+        <v>404</v>
       </c>
       <c r="L25" t="n">
-        <v>400.7592675020414</v>
+        <v>404</v>
       </c>
       <c r="M25" t="n">
         <v>404</v>
@@ -29304,22 +29304,22 @@
         <v>404</v>
       </c>
       <c r="T25" t="n">
-        <v>404</v>
+        <v>209.3696484734708</v>
       </c>
       <c r="U25" t="n">
         <v>150.9500306187202</v>
       </c>
       <c r="V25" t="n">
-        <v>404</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
-        <v>404</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X25" t="n">
         <v>404</v>
       </c>
       <c r="Y25" t="n">
-        <v>404</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="26">
@@ -29414,7 +29414,7 @@
         <v>314</v>
       </c>
       <c r="D27" t="n">
-        <v>182.5561359885369</v>
+        <v>314</v>
       </c>
       <c r="E27" t="n">
         <v>314</v>
@@ -29459,7 +29459,7 @@
         <v>314</v>
       </c>
       <c r="S27" t="n">
-        <v>314</v>
+        <v>182.5561359884892</v>
       </c>
       <c r="T27" t="n">
         <v>314</v>
@@ -29544,7 +29544,7 @@
         <v>314</v>
       </c>
       <c r="U28" t="n">
-        <v>301.2006489241123</v>
+        <v>301.2006489241609</v>
       </c>
       <c r="V28" t="n">
         <v>314</v>
@@ -29666,7 +29666,7 @@
         <v>314</v>
       </c>
       <c r="I30" t="n">
-        <v>79.38771055913075</v>
+        <v>79.38771055908289</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29739,7 +29739,7 @@
         <v>314</v>
       </c>
       <c r="G31" t="n">
-        <v>314</v>
+        <v>301.2006489241609</v>
       </c>
       <c r="H31" t="n">
         <v>314</v>
@@ -29781,7 +29781,7 @@
         <v>314</v>
       </c>
       <c r="U31" t="n">
-        <v>301.2006489241123</v>
+        <v>314</v>
       </c>
       <c r="V31" t="n">
         <v>314</v>
@@ -29885,7 +29885,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>283.4798166368616</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29930,7 +29930,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>207.922287858412</v>
+        <v>417</v>
       </c>
       <c r="S33" t="n">
         <v>417</v>
@@ -29939,19 +29939,19 @@
         <v>404.6208312552496</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1983314582999</v>
+        <v>72.19833145829996</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>86.51066719152016</v>
       </c>
       <c r="W33" t="n">
+        <v>133.164931495139</v>
+      </c>
+      <c r="X33" t="n">
         <v>417</v>
       </c>
-      <c r="X33" t="n">
-        <v>91.86273944538615</v>
-      </c>
       <c r="Y33" t="n">
-        <v>71.39139276613295</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -29961,19 +29961,19 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C34" t="n">
         <v>417</v>
       </c>
-      <c r="C34" t="n">
-        <v>272.7252466480447</v>
-      </c>
       <c r="D34" t="n">
-        <v>285.5362180555555</v>
+        <v>417</v>
       </c>
       <c r="E34" t="n">
         <v>417</v>
       </c>
       <c r="F34" t="n">
-        <v>417</v>
+        <v>277.6104227972858</v>
       </c>
       <c r="G34" t="n">
         <v>417</v>
@@ -29988,7 +29988,7 @@
         <v>24.43214555721923</v>
       </c>
       <c r="K34" t="n">
-        <v>270.7125770798316</v>
+        <v>417</v>
       </c>
       <c r="L34" t="n">
         <v>400.7592675020414</v>
@@ -30015,19 +30015,19 @@
         <v>359.7022501946587</v>
       </c>
       <c r="T34" t="n">
-        <v>209.3696484734708</v>
+        <v>417</v>
       </c>
       <c r="U34" t="n">
-        <v>368.9767085487833</v>
+        <v>150.9500306187202</v>
       </c>
       <c r="V34" t="n">
-        <v>199.1703102162162</v>
+        <v>417</v>
       </c>
       <c r="W34" t="n">
-        <v>417</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
-        <v>417</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y34" t="n">
         <v>417</v>
@@ -30119,19 +30119,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>87.99074523163711</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>36.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>22.93768689770263</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>14.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.5567056863481</v>
@@ -30182,13 +30182,13 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>107.3731429098285</v>
+        <v>418</v>
       </c>
       <c r="X36" t="n">
         <v>418</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>117.1987242612734</v>
       </c>
     </row>
     <row r="37">
@@ -30201,34 +30201,34 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>418</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>418</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>418</v>
       </c>
       <c r="F37" t="n">
         <v>418</v>
       </c>
       <c r="G37" t="n">
+        <v>244.8905941530055</v>
+      </c>
+      <c r="H37" t="n">
         <v>418</v>
       </c>
-      <c r="H37" t="n">
-        <v>227.4083392163727</v>
-      </c>
       <c r="I37" t="n">
-        <v>418</v>
+        <v>315.9263580077506</v>
       </c>
       <c r="J37" t="n">
-        <v>349.4321455572193</v>
+        <v>24.43214555721923</v>
       </c>
       <c r="K37" t="n">
         <v>270.7125770798316</v>
       </c>
       <c r="L37" t="n">
-        <v>418</v>
+        <v>400.7592675020414</v>
       </c>
       <c r="M37" t="n">
         <v>418</v>
@@ -30249,7 +30249,7 @@
         <v>418</v>
       </c>
       <c r="S37" t="n">
-        <v>374.83026072302</v>
+        <v>359.7022501946587</v>
       </c>
       <c r="T37" t="n">
         <v>209.3696484734708</v>
@@ -30258,10 +30258,10 @@
         <v>150.9500306187202</v>
       </c>
       <c r="V37" t="n">
-        <v>199.1703102162162</v>
+        <v>418</v>
       </c>
       <c r="W37" t="n">
-        <v>418</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
         <v>418</v>
@@ -30365,10 +30365,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>17.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>14.63624233787687</v>
       </c>
       <c r="G39" t="n">
         <v>325.5567056863481</v>
@@ -30377,7 +30377,7 @@
         <v>330.40233246944</v>
       </c>
       <c r="I39" t="n">
-        <v>58.72974478422695</v>
+        <v>210.8315745705938</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,13 +30401,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>149.7411518829324</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>418</v>
       </c>
       <c r="S39" t="n">
-        <v>138.1680093985736</v>
+        <v>418</v>
       </c>
       <c r="T39" t="n">
         <v>404.6208312552496</v>
@@ -30416,16 +30416,16 @@
         <v>400.1983314582999</v>
       </c>
       <c r="V39" t="n">
-        <v>89.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
         <v>418</v>
       </c>
       <c r="X39" t="n">
-        <v>418</v>
+        <v>135.8073314951391</v>
       </c>
       <c r="Y39" t="n">
-        <v>74.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>418</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
         <v>272.7252466480447</v>
@@ -30447,25 +30447,25 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>418</v>
       </c>
       <c r="G40" t="n">
         <v>244.8905941530055</v>
       </c>
       <c r="H40" t="n">
-        <v>227.4083392163727</v>
+        <v>418</v>
       </c>
       <c r="I40" t="n">
-        <v>418</v>
+        <v>172.0239474233969</v>
       </c>
       <c r="J40" t="n">
-        <v>24.43214555721923</v>
+        <v>271.1296875464426</v>
       </c>
       <c r="K40" t="n">
-        <v>418</v>
+        <v>270.7125770798316</v>
       </c>
       <c r="L40" t="n">
-        <v>418</v>
+        <v>400.7592675020414</v>
       </c>
       <c r="M40" t="n">
         <v>418</v>
@@ -30486,22 +30486,22 @@
         <v>418</v>
       </c>
       <c r="S40" t="n">
-        <v>418</v>
+        <v>359.7022501946587</v>
       </c>
       <c r="T40" t="n">
         <v>418</v>
       </c>
       <c r="U40" t="n">
+        <v>150.9500306187202</v>
+      </c>
+      <c r="V40" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W40" t="n">
         <v>418</v>
       </c>
-      <c r="V40" t="n">
-        <v>275.5220749082352</v>
-      </c>
-      <c r="W40" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X40" t="n">
-        <v>247.4436454301076</v>
+        <v>418</v>
       </c>
       <c r="Y40" t="n">
         <v>418</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>149.7411518829602</v>
+        <v>149.7411518829324</v>
       </c>
       <c r="R42" t="n">
         <v>309</v>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>276.176839246739</v>
+      </c>
+      <c r="K2" t="n">
         <v>344</v>
       </c>
-      <c r="K2" t="n">
-        <v>43.46660804020098</v>
-      </c>
       <c r="L2" t="n">
-        <v>53.92417085427138</v>
+        <v>53.92417085427132</v>
       </c>
       <c r="M2" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>344</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>48.85105553720804</v>
+        <v>344</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.8591756693296</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,7 +34822,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>142.4820496339021</v>
+        <v>78.69710481719957</v>
       </c>
       <c r="K3" t="n">
         <v>220.6269206785272</v>
@@ -34840,7 +34840,7 @@
         <v>284.9569747329351</v>
       </c>
       <c r="P3" t="n">
-        <v>84.79360686776201</v>
+        <v>148.5785516844645</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34895,10 +34895,10 @@
         <v>160.1094058469945</v>
       </c>
       <c r="H4" t="n">
-        <v>69.96944454507009</v>
+        <v>177.5916607836273</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>232.9760525766031</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34907,7 +34907,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.240732497958561</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,19 +34931,19 @@
         <v>45.29774980534131</v>
       </c>
       <c r="T4" t="n">
-        <v>195.6303515265292</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>205.8296897837838</v>
+        <v>77.69187558859197</v>
       </c>
       <c r="W4" t="n">
-        <v>178.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>157.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34965,7 +34965,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.310670694506807e-14</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -34989,7 +34989,7 @@
         <v>53.92417085427138</v>
       </c>
       <c r="M5" t="n">
-        <v>183.8591756693298</v>
+        <v>344</v>
       </c>
       <c r="N5" t="n">
         <v>344</v>
@@ -35001,7 +35001,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q5" t="n">
-        <v>344</v>
+        <v>183.8591756693296</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35065,10 +35065,10 @@
         <v>220.6269206785272</v>
       </c>
       <c r="L6" t="n">
-        <v>313.7887810090643</v>
+        <v>250.0038361923617</v>
       </c>
       <c r="M6" t="n">
-        <v>69.49009734780162</v>
+        <v>133.2750421645043</v>
       </c>
       <c r="N6" t="n">
         <v>182.1776350143152</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.23782483801586</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>73.06146581373972</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>119.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>124.0190951630435</v>
@@ -35141,7 +35141,7 @@
         <v>344</v>
       </c>
       <c r="K7" t="n">
-        <v>134.2874229201684</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>357.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>43.46660804020104</v>
+        <v>43.466608040201</v>
       </c>
       <c r="L8" t="n">
-        <v>53.92417085427138</v>
+        <v>250.2580939983669</v>
       </c>
       <c r="M8" t="n">
-        <v>196.3339231440769</v>
+        <v>357.0000000000005</v>
       </c>
       <c r="N8" t="n">
-        <v>357.0000000000001</v>
+        <v>357.0000000000005</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q8" t="n">
-        <v>357.0000000000001</v>
+        <v>357.0000000000005</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,7 +35296,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>130.171852291947</v>
+        <v>142.4820496339021</v>
       </c>
       <c r="K9" t="n">
         <v>220.6269206785272</v>
@@ -35314,7 +35314,7 @@
         <v>284.9569747329351</v>
       </c>
       <c r="P9" t="n">
-        <v>148.5785516844645</v>
+        <v>136.2683543425293</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>117.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>132.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2.449450572520379</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -35375,13 +35375,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>357.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>134.2874229201684</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.240732497958533</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>45.29774980534128</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>161.4648192717381</v>
+        <v>195.6303515265292</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>254.0499693812798</v>
       </c>
       <c r="V10" t="n">
         <v>205.8296897837838</v>
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>360.0000000000023</v>
+        <v>360.0000000000037</v>
       </c>
       <c r="K11" t="n">
         <v>43.46660804020104</v>
@@ -35463,10 +35463,10 @@
         <v>53.92417085427138</v>
       </c>
       <c r="M11" t="n">
-        <v>360.0000000000023</v>
+        <v>360.0000000000037</v>
       </c>
       <c r="N11" t="n">
-        <v>360.0000000000023</v>
+        <v>360.0000000000037</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35475,7 +35475,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q11" t="n">
-        <v>199.2127110228579</v>
+        <v>199.2127110229027</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35545,10 +35545,10 @@
         <v>133.2750421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>182.1776350143152</v>
+        <v>181.7462255511969</v>
       </c>
       <c r="O12" t="n">
-        <v>284.5255652698251</v>
+        <v>284.9569747329351</v>
       </c>
       <c r="P12" t="n">
         <v>148.5785516844645</v>
@@ -35588,10 +35588,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.41215656279736</v>
+        <v>107.8861996629213</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>122.2747533519553</v>
       </c>
       <c r="D13" t="n">
         <v>109.4637819444445</v>
@@ -35603,7 +35603,7 @@
         <v>120.6171440322581</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>150.1094058469945</v>
       </c>
       <c r="H13" t="n">
         <v>167.5916607836273</v>
@@ -35612,10 +35612,10 @@
         <v>222.9760525766031</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.374924797343499</v>
       </c>
       <c r="K13" t="n">
-        <v>124.2874229201684</v>
+        <v>124.2874229201698</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35639,22 +35639,22 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>35.29774980534128</v>
       </c>
       <c r="T13" t="n">
-        <v>185.6303515265292</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>195.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>168.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>147.5563545698924</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -35694,16 +35694,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>43.46660804020101</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="L14" t="n">
-        <v>253.1368818771307</v>
+        <v>53.92417085427138</v>
       </c>
       <c r="M14" t="n">
-        <v>360.0000000000019</v>
+        <v>360.0000000000032</v>
       </c>
       <c r="N14" t="n">
-        <v>360.0000000000019</v>
+        <v>360.0000000000032</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35712,7 +35712,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q14" t="n">
-        <v>360.0000000000019</v>
+        <v>242.6793190630959</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35785,7 +35785,7 @@
         <v>182.1776350143152</v>
       </c>
       <c r="O15" t="n">
-        <v>284.5255652697679</v>
+        <v>284.5255652698168</v>
       </c>
       <c r="P15" t="n">
         <v>148.5785516844645</v>
@@ -35828,13 +35828,13 @@
         <v>107.8861996629213</v>
       </c>
       <c r="C16" t="n">
-        <v>122.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>109.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>114.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -35843,10 +35843,10 @@
         <v>150.1094058469945</v>
       </c>
       <c r="H16" t="n">
-        <v>167.5916607836273</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>70.80628409432917</v>
+        <v>222.9760525766031</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -35882,10 +35882,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>244.0499693812798</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>117.1295533795656</v>
       </c>
       <c r="W16" t="n">
         <v>168.6271901612903</v>
@@ -35934,13 +35934,13 @@
         <v>43.46660804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>253.1368818771321</v>
+        <v>253.1368818771749</v>
       </c>
       <c r="M17" t="n">
-        <v>360.0000000000014</v>
+        <v>360.0000000000023</v>
       </c>
       <c r="N17" t="n">
-        <v>360.0000000000014</v>
+        <v>360.0000000000023</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q17" t="n">
-        <v>360.0000000000014</v>
+        <v>360.0000000000023</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36019,10 +36019,10 @@
         <v>133.2750421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>181.746225551148</v>
+        <v>182.1776350143152</v>
       </c>
       <c r="O18" t="n">
-        <v>284.9569747329351</v>
+        <v>284.5255652698136</v>
       </c>
       <c r="P18" t="n">
         <v>148.5785516844645</v>
@@ -36071,10 +36071,10 @@
         <v>118.4637819444445</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>123.0190951630435</v>
       </c>
       <c r="F19" t="n">
-        <v>129.6171440322581</v>
+        <v>3.881649683764197</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -36083,13 +36083,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>231.9760525766031</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>328.8278858147119</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>133.2874229201684</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36113,16 +36113,16 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>44.29774980534131</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>194.6303515265292</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>253.0499693812798</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>204.8296897837838</v>
       </c>
       <c r="W19" t="n">
         <v>177.6271901612903</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>360.0000000000015</v>
+        <v>360.0000000000024</v>
       </c>
       <c r="K20" t="n">
-        <v>43.46660804020104</v>
+        <v>360.0000000000124</v>
       </c>
       <c r="L20" t="n">
-        <v>53.92417085427144</v>
+        <v>53.92417085427132</v>
       </c>
       <c r="M20" t="n">
-        <v>360.0000000000015</v>
+        <v>360.0000000000024</v>
       </c>
       <c r="N20" t="n">
-        <v>360.0000000000015</v>
+        <v>242.6793190630952</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -36186,7 +36186,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q20" t="n">
-        <v>199.2127110228604</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36259,7 +36259,7 @@
         <v>182.1776350143152</v>
       </c>
       <c r="O21" t="n">
-        <v>284.5255652697679</v>
+        <v>284.5255652698168</v>
       </c>
       <c r="P21" t="n">
         <v>148.5785516844645</v>
@@ -36299,19 +36299,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>116.8861996629213</v>
       </c>
       <c r="C22" t="n">
-        <v>131.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>118.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>123.0190951630435</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>129.6171440322581</v>
       </c>
       <c r="G22" t="n">
         <v>159.1094058469945</v>
@@ -36320,16 +36320,16 @@
         <v>176.5916607836273</v>
       </c>
       <c r="I22" t="n">
-        <v>231.9760525766031</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>133.2874229201684</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3.240732497958561</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -36350,19 +36350,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>44.29774980534131</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>96.62786901682983</v>
+        <v>7.18904331000416</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>204.8296897837838</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>177.6271901612903</v>
       </c>
       <c r="X22" t="n">
         <v>156.5563545698924</v>
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>360.0000000000031</v>
       </c>
       <c r="K23" t="n">
-        <v>43.46660804020101</v>
+        <v>360.0000000000123</v>
       </c>
       <c r="L23" t="n">
-        <v>53.92417085427135</v>
+        <v>53.92417085427132</v>
       </c>
       <c r="M23" t="n">
-        <v>248.0637665600675</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>242.6793190630921</v>
       </c>
       <c r="O23" t="n">
-        <v>360.0000000000018</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>360.0000000000018</v>
+        <v>48.85105553720804</v>
       </c>
       <c r="Q23" t="n">
-        <v>360.0000000000018</v>
+        <v>360.0000000000031</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36496,7 +36496,7 @@
         <v>182.1776350143152</v>
       </c>
       <c r="O24" t="n">
-        <v>284.5255652698211</v>
+        <v>284.5255652698124</v>
       </c>
       <c r="P24" t="n">
         <v>148.5785516844645</v>
@@ -36536,37 +36536,37 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>131.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>123.0190951630435</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>159.1094058469945</v>
       </c>
       <c r="H25" t="n">
         <v>176.5916607836273</v>
       </c>
       <c r="I25" t="n">
-        <v>48.73183366847464</v>
+        <v>231.9760525766031</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>339.8819563007241</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>133.2874229201684</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.240732497958533</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -36590,22 +36590,22 @@
         <v>44.29774980534128</v>
       </c>
       <c r="T25" t="n">
-        <v>194.6303515265292</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>204.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>177.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>156.5563545698924</v>
       </c>
       <c r="Y25" t="n">
-        <v>116.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>43.46660804020104</v>
+        <v>43.46660804020101</v>
       </c>
       <c r="L26" t="n">
-        <v>53.92417085427138</v>
+        <v>234.904558644825</v>
       </c>
       <c r="M26" t="n">
-        <v>180.9803877905419</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="N26" t="n">
-        <v>341</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -36660,7 +36660,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q26" t="n">
-        <v>341</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36727,7 +36727,7 @@
         <v>313.7887810090643</v>
       </c>
       <c r="M27" t="n">
-        <v>57.61130946901375</v>
+        <v>133.2750421645043</v>
       </c>
       <c r="N27" t="n">
         <v>182.1776350143152</v>
@@ -36736,7 +36736,7 @@
         <v>284.9569747329351</v>
       </c>
       <c r="P27" t="n">
-        <v>148.5785516844645</v>
+        <v>72.91481898902282</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36830,7 +36830,7 @@
         <v>104.6303515265292</v>
       </c>
       <c r="U28" t="n">
-        <v>150.250618305392</v>
+        <v>150.2506183054407</v>
       </c>
       <c r="V28" t="n">
         <v>114.8296897837838</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>341.0000000000001</v>
+        <v>43.46660804020101</v>
       </c>
       <c r="L29" t="n">
-        <v>53.92417085427132</v>
+        <v>234.904558644825</v>
       </c>
       <c r="M29" t="n">
-        <v>224.4469958307429</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="N29" t="n">
-        <v>341</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>341.0000000000123</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36973,7 +36973,7 @@
         <v>284.9569747329351</v>
       </c>
       <c r="P30" t="n">
-        <v>72.91481898897391</v>
+        <v>72.91481898902282</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -37025,7 +37025,7 @@
         <v>39.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>69.10940584699456</v>
+        <v>56.31005477115549</v>
       </c>
       <c r="H31" t="n">
         <v>86.59166078362728</v>
@@ -37067,7 +37067,7 @@
         <v>104.6303515265292</v>
       </c>
       <c r="U31" t="n">
-        <v>150.250618305392</v>
+        <v>163.0499693812798</v>
       </c>
       <c r="V31" t="n">
         <v>114.8296897837838</v>
@@ -37119,22 +37119,22 @@
         <v>43.46660804020101</v>
       </c>
       <c r="L32" t="n">
-        <v>53.92417085427137</v>
+        <v>222.4298111700657</v>
       </c>
       <c r="M32" t="n">
-        <v>328.0000000000014</v>
+        <v>328</v>
       </c>
       <c r="N32" t="n">
-        <v>328.0000000000014</v>
+        <v>328</v>
       </c>
       <c r="O32" t="n">
-        <v>328.0000000000014</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>48.85105553720804</v>
       </c>
       <c r="Q32" t="n">
-        <v>168.5056403157901</v>
+        <v>328</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
         <v>220.6269206785272</v>
       </c>
       <c r="L33" t="n">
-        <v>186.6503008388264</v>
+        <v>313.7887810090643</v>
       </c>
       <c r="M33" t="n">
         <v>133.2750421645043</v>
@@ -37207,7 +37207,7 @@
         <v>182.1776350143152</v>
       </c>
       <c r="O33" t="n">
-        <v>284.9569747329351</v>
+        <v>157.8184945626971</v>
       </c>
       <c r="P33" t="n">
         <v>148.5785516844645</v>
@@ -37247,19 +37247,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>129.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>144.2747533519553</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>131.4637819444445</v>
       </c>
       <c r="E34" t="n">
         <v>136.0190951630435</v>
       </c>
       <c r="F34" t="n">
-        <v>142.6171440322581</v>
+        <v>3.227566829543844</v>
       </c>
       <c r="G34" t="n">
         <v>172.1094058469945</v>
@@ -37274,7 +37274,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>146.2874229201684</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37301,19 +37301,19 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>207.6303515265292</v>
       </c>
       <c r="U34" t="n">
-        <v>218.026677930063</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>217.8296897837838</v>
       </c>
       <c r="W34" t="n">
-        <v>190.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>169.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>129.5346471505376</v>
@@ -37353,10 +37353,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>43.46660804020102</v>
+        <v>325</v>
       </c>
       <c r="L35" t="n">
-        <v>325</v>
+        <v>53.92417085427138</v>
       </c>
       <c r="M35" t="n">
         <v>325</v>
@@ -37371,7 +37371,7 @@
         <v>48.85105553720804</v>
       </c>
       <c r="Q35" t="n">
-        <v>219.5510232912777</v>
+        <v>209.0934604772075</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,13 +37441,13 @@
         <v>133.2750421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>182.1776350143152</v>
+        <v>43.16036696528933</v>
       </c>
       <c r="O36" t="n">
         <v>284.9569747329351</v>
       </c>
       <c r="P36" t="n">
-        <v>9.561283635438752</v>
+        <v>148.5785516844645</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37487,34 +37487,34 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>145.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>132.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>137.0190951630435</v>
       </c>
       <c r="F37" t="n">
         <v>143.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>173.1094058469945</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>190.5916607836273</v>
       </c>
       <c r="I37" t="n">
-        <v>245.9760525766031</v>
+        <v>143.9024105843536</v>
       </c>
       <c r="J37" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>17.24073249795856</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,7 +37535,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>15.12801052836131</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -37544,10 +37544,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>218.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>191.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>170.5563545698924</v>
@@ -37590,25 +37590,25 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>43.46660804020102</v>
+        <v>325</v>
       </c>
       <c r="L38" t="n">
-        <v>53.92417085427135</v>
+        <v>53.92417085427138</v>
       </c>
       <c r="M38" t="n">
-        <v>214.4779079742145</v>
+        <v>209.0934604772074</v>
       </c>
       <c r="N38" t="n">
         <v>325</v>
       </c>
       <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>48.85105553720804</v>
+      </c>
+      <c r="Q38" t="n">
         <v>325</v>
-      </c>
-      <c r="P38" t="n">
-        <v>325</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37672,10 +37672,10 @@
         <v>220.6269206785272</v>
       </c>
       <c r="L39" t="n">
-        <v>174.7715129600385</v>
+        <v>308.0465551245427</v>
       </c>
       <c r="M39" t="n">
-        <v>133.2750421645043</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>182.1776350143152</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>130.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -37733,25 +37733,25 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>143.6171440322581</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>190.5916607836273</v>
       </c>
       <c r="I40" t="n">
-        <v>245.9760525766031</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>246.6975419892234</v>
       </c>
       <c r="K40" t="n">
-        <v>147.2874229201684</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>17.24073249795853</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37772,22 +37772,22 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>58.29774980534128</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>208.6303515265292</v>
       </c>
       <c r="U40" t="n">
-        <v>267.0499693812798</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>76.35176469201899</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>191.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>170.5563545698924</v>
       </c>
       <c r="Y40" t="n">
         <v>130.5346471505376</v>
@@ -37833,16 +37833,16 @@
         <v>53.92417085427138</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>165.6268524370064</v>
       </c>
       <c r="O41" t="n">
-        <v>214.4779079742144</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>325</v>
+        <v>48.85105553720804</v>
       </c>
       <c r="Q41" t="n">
         <v>325</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>142.4820496339021</v>
+        <v>3.464781584876341</v>
       </c>
       <c r="K42" t="n">
         <v>220.6269206785272</v>
@@ -37921,10 +37921,10 @@
         <v>284.9569747329351</v>
       </c>
       <c r="P42" t="n">
-        <v>9.561283635438752</v>
+        <v>148.5785516844645</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.779011588750614e-11</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -38067,7 +38067,7 @@
         <v>43.46660804020102</v>
       </c>
       <c r="L44" t="n">
-        <v>53.92417085427135</v>
+        <v>219.5510232912778</v>
       </c>
       <c r="M44" t="n">
         <v>325</v>
@@ -38076,13 +38076,13 @@
         <v>325</v>
       </c>
       <c r="O44" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>48.85105553720804</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.6268524370064</v>
+        <v>325</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>142.4820496339021</v>
+        <v>3.464781584876341</v>
       </c>
       <c r="K45" t="n">
         <v>220.6269206785272</v>
@@ -38158,7 +38158,7 @@
         <v>284.9569747329351</v>
       </c>
       <c r="P45" t="n">
-        <v>9.561283635438752</v>
+        <v>148.5785516844645</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
